--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AXI to CAMs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scheduler both dirs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps arbiter" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps bank timer" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps refresh+top" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,22 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +118,18 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -124,11 +151,17 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,6 +198,31 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -559,6 +617,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1285,7 +1344,7 @@
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>*** SUSPECT: on-board reads show device-word SHIFT (0x..a5a0) + phase1==phase0 -&gt; de-interleave order wrong in pumice_rd_intake. beats_mismatched==2*txn ***</t>
+          <t>RESOLVED 2026-07-22: the on-board device-word/shift story was host config + measurement (see #39 close-out) — read path clean at the bring-up tuple (wrlat=1/rden=6/rdly=7). Remaining integrity issue = runtime config axes, #42.</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1994,7 @@
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>*** SUSPECT: the word-&gt;AXI-beat device-word de-interleave here/rd_intake is wrong ***</t>
+          <t>RESOLVED 2026-07-22: the on-board device-word/shift story was host config + measurement (see #39 close-out) — read path clean at the bring-up tuple (wrlat=1/rden=6/rdly=7). Remaining integrity issue = runtime config axes, #42.</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2099,6 +2158,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2722,7 +2782,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>REF emitted every t_refi; all banks precharged before REF</t>
+          <t>REF emitted every t_refi; REF only under w_ref_safe (rows closed + nothing in flight/guarded + prior tRFC elapsed); drain REFs tRFC-spaced</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -2835,7 +2895,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>CAS latency / CAS write latency / burst length shadow, drives DFI read/write timing.</t>
+          <t>CAS latency / CAS write latency / burst length shadow from the MR writes. RTL reset = BL8 (MR0.VAL 0x0433); the Nexys board runtime-programs BL4 (0x0432).</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2886,6 +2946,326 @@
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Refresh iface</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>refresh_req_i / refresh_drain_i</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>refresh_ctrl</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Owed-refresh request (pending&gt;0) and burst-drain hold.</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>req high =&gt; arbiter priority-2 branch; columns/ACTs starve by design while high</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Refresh iface</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>refresh_grant_o</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Pulsed when the REF command FIRES (w_fire_out &amp;&amp; r_grant).</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>one grant per issued REF; decrements pending + drain quota</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Timing cfg</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>t_rfc_i</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>CSR (TIMINGS_RFC_REFI.tRFC)</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Mission-mode REF-&gt;ACT/REF recovery, MC cycles (reset 16). Loaded into the arbiter's r_rfc_cnt on each fired REF.</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>no ACT or REF while r_rfc_cnt != 0 (w_rfc_busy) — audited by the history checker's positional tRFC check</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>added 2026-07-21: previously enforced by NOTHING in mission mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>DV hooks</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>CMD_HISTORY_EN / HIST_T_*</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>In-scheduler command-history scoreboard (audit-only shift registers on the ISSUED stream; $fatal assertions, sim-only).</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>default 0 = zero cost; -GCMD_HISTORY_EN=1 + --assert in DV</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>moved into the scheduler 2026-07-22 (was a TB bind)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Refresh iface</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>refresh_req_i / refresh_drain_i</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>refresh_ctrl</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Owed-refresh request (pending&gt;0) and burst-drain hold.</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>req high =&gt; arbiter priority-2 branch; columns/ACTs starve by design while high</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Refresh iface</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>refresh_grant_o</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Pulsed when the REF command FIRES (w_fire_out &amp;&amp; r_grant).</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>one grant per issued REF; decrements pending + drain quota</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Timing cfg</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>t_rfc_i</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>CSR (TIMINGS_RFC_REFI.tRFC)</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Mission-mode REF-&gt;ACT/REF recovery, MC cycles (reset 16). Loaded into the arbiter's r_rfc_cnt on each fired REF.</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>no ACT or REF while r_rfc_cnt != 0 (w_rfc_busy) — audited by the history checker's positional tRFC check</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>added 2026-07-21: previously enforced by NOTHING in mission mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>DV hooks</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>CMD_HISTORY_EN / HIST_T_*</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>In-scheduler command-history scoreboard (audit-only shift registers on the ISSUED stream; $fatal assertions, sim-only).</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>default 0 = zero cost; -GCMD_HISTORY_EN=1 + --assert in DV</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>moved into the scheduler 2026-07-22 (was a TB bind)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2894,4 +3274,3451 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E185"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter — decision K-maps (rtl/fub/pumice_cmd_arbiter.sv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Each grid is computed from a python mirror of the exact RTL expression. Variables are the 1-bit conditions feeding the decision (counter==0 flags etc.). Gray order 00 01 11 10; &gt;4 vars page into multiple grids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Healthy shapes are stated per map — a regression that opens an illegal cell is visible by inspection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>w_ref_safe</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (refresh pick gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>w_ref_safe = !w_any_active &amp;&amp; !w_inflight_preact &amp;&amp; (r_guard0=='0) &amp;&amp; (r_guard1=='0) &amp;&amp; !w_rfc_busy   [guards collapsed: guards_nz = |r_guard0 | |r_guard1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rows = any_active/inflight_preact   cols = guards_nz/rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros. Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>refresh-branch action (given refresh_req_i||refresh_drain_i)</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (priority 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>if (any_active) { if (rfsh_pre_found) PRE else wait } else if (ref_safe) REF else wait</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>rows = any_active/rfsh_pre_found   cols = ref_safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>rd_col_m[e]  (given rd_sch_valid_i[e])</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>rd_col_m = rhit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; twtr_ok &amp;&amp; rd_issue_ready &amp;&amp; !w_inflight_col</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = rd_issue_ready/inflight_col</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [rd_issue_ready=1, inflight_col=0], and there only the all-ones cell. A 1 on any other page = a column issued with the issue-FIFO full (double-issue) or tCCD overrun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>[rd_issue_ready=0, inflight_col=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>[rd_issue_ready=0, inflight_col=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>[rd_issue_ready=1, inflight_col=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>[rd_issue_ready=1, inflight_col=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>wr_col_m[e]  (given wr_sch_valid_i[e])</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>wr_col_m = whit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; trtw_ok &amp;&amp; wr_commit_ready &amp;&amp; !w_inflight_col</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = wr_commit_ready/inflight_col</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Mirror of rd_col_m: single 1-cell on the [commit_ready=1, inflight_col=0] page only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>[wr_commit_ready=0, inflight_col=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>[wr_commit_ready=0, inflight_col=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>[wr_commit_ready=1, inflight_col=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>[wr_commit_ready=1, inflight_col=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>act_m = !bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; bank_act_ready &amp;&amp; tfaw_ok &amp;&amp; trrd_ok &amp;&amp; !w_rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B112" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B114" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B118" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B120" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D124" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B126" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B128" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>pre_m = bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; !hit &amp;&amp; bank_pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>rows = row_active/guarded   cols = hit/pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D136" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E136" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B138" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B140" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>w_guarded[b]</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [bank_match = r_bank==b]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>rows = guard0/guard1   cols = inflight_rowop_or_col/bank_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D148" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B149" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B150" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B151" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>w_out_ready / w_fire_out</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (output register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B161" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B162" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B163" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
+        <is>
+          <t>pick priority (strict, first match wins)</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="23" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C169" s="23" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D169" s="23" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B170" s="24" t="inlineStr">
+        <is>
+          <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
+        </is>
+      </c>
+      <c r="C170" s="24" t="inlineStr">
+        <is>
+          <t>forward init op</t>
+        </is>
+      </c>
+      <c r="D170" s="24" t="inlineStr">
+        <is>
+          <t>MRS/PRE/REF from init_sequencer verbatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B171" s="24" t="inlineStr">
+        <is>
+          <t>refresh_req_i || refresh_drain_i</t>
+        </is>
+      </c>
+      <c r="C171" s="24" t="inlineStr">
+        <is>
+          <t>refresh branch</t>
+        </is>
+      </c>
+      <c r="D171" s="24" t="inlineStr">
+        <is>
+          <t>see refresh-branch K-map; never falls through while pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>rd_col_f</t>
+        </is>
+      </c>
+      <c r="C172" s="24" t="inlineStr">
+        <is>
+          <t>RD/RDA row-hit</t>
+        </is>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
+        <is>
+          <t>read priority over write</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B173" s="24" t="inlineStr">
+        <is>
+          <t>wr_col_f</t>
+        </is>
+      </c>
+      <c r="C173" s="24" t="inlineStr">
+        <is>
+          <t>WR/WRA row-hit</t>
+        </is>
+      </c>
+      <c r="D173" s="24" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B174" s="24" t="inlineStr">
+        <is>
+          <t>rd_act_f</t>
+        </is>
+      </c>
+      <c r="C174" s="24" t="inlineStr">
+        <is>
+          <t>ACT for oldest pending read</t>
+        </is>
+      </c>
+      <c r="D174" s="24" t="inlineStr">
+        <is>
+          <t>bank-parallel</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B175" s="24" t="inlineStr">
+        <is>
+          <t>wr_act_f</t>
+        </is>
+      </c>
+      <c r="C175" s="24" t="inlineStr">
+        <is>
+          <t>ACT for oldest pending write</t>
+        </is>
+      </c>
+      <c r="D175" s="24" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B176" s="24" t="inlineStr">
+        <is>
+          <t>rd_pre_f</t>
+        </is>
+      </c>
+      <c r="C176" s="24" t="inlineStr">
+        <is>
+          <t>PRE wrong-row bank (read)</t>
+        </is>
+      </c>
+      <c r="D176" s="24" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B177" s="24" t="inlineStr">
+        <is>
+          <t>wr_pre_f</t>
+        </is>
+      </c>
+      <c r="C177" s="24" t="inlineStr">
+        <is>
+          <t>PRE wrong-row bank (write)</t>
+        </is>
+      </c>
+      <c r="D177" s="24" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="inlineStr">
+        <is>
+          <t>r_rfc_cnt next-value</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="inlineStr">
+        <is>
+          <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="23" t="inlineStr">
+        <is>
+          <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
+        </is>
+      </c>
+      <c r="B182" s="23" t="inlineStr">
+        <is>
+          <t>r_rfc_cnt != 0</t>
+        </is>
+      </c>
+      <c r="C182" s="23" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B183" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C183" s="24" t="inlineStr">
+        <is>
+          <t>t_rfc_i (load)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B184" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="24" t="inlineStr">
+        <is>
+          <t>r_rfc_cnt - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B185" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C185" s="24" t="inlineStr">
+        <is>
+          <t>0 (idle)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>bank_timer — safe-signal K-maps (rtl/fub/bank_timer.sv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Flags: rv=r_row_valid, ap=r_ap_pending, X0=(timer X == 0). safe_* are pure combinational ANDs over these — one register stage (the counters) behind, which is why the arbiter carries the 2-cycle guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>safe_act_o</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:133</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>safe_act = !r_row_valid &amp;&amp; (r_rp == 0) &amp;&amp; (r_rc == 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rows = row_valid/rp==0   cols = rc==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (0,1,1): closed row, tRP and tRC elapsed. Any 1 with row_valid=1 would re-ACT an open bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>safe_rd_o / safe_wr_o</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:135-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>safe_rd = safe_wr = r_row_valid &amp;&amp; (r_rcd == 0) &amp;&amp; !r_ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>rows = row_valid/rcd==0   cols = ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). ap_pending=1 must kill columns — the row is committed to auto-close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>safe_pre_o</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:138</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>safe_pre = r_row_valid &amp;&amp; (r_ras == 0) &amp;&amp; (r_preblk == 0) &amp;&amp; !r_ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>rows = row_valid/ras==0   cols = preblk==0/ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>w_ap_fire (internal auto-precharge)</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:88</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>w_ap_fire = r_ap_pending &amp;&amp; (r_preblk == 0) &amp;&amp; (r_ras == 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>rows = ap_pending/preblk==0   cols = ras==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>state_o (observability only)</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:144-147</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>rv ? (rcd_nz ? ACTIVATING : ACTIVE) : (rp_nz ? PRECHARGING : IDLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>rows = row_valid/rcd_nz   cols = rp_nz</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>row_valid / ap_pending next-state priority</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:115-127</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>Strict priority ACT &gt; PRE &gt; auto-PRE &gt; column. The arbiter never issues ACT and PRE to one bank in one cycle (single-issue), so rows 1-2 cannot conflict in practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>set_act</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>set_pre</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>w_ap_fire</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>set_rd||set_wr</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>row_valid'</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>ap_pending'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>1 (row=row_i)</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>set_ap_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>refresh_ctrl + scheduler top — K-maps (rtl/fub/refresh_ctrl.sv, rtl/macro/pumice_mem_cmd_scheduler.sv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Flags: pend_nz=(r_pending&gt;0), rem_nz=(r_burst_remaining&gt;0), expired=(r_refi_cnt==0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>w_grant_accept</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>refresh_ctrl.sv:79</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>w_grant_accept = refresh_grant_i &amp;&amp; (r_pending &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = grant/pend_nz   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a grant with nothing pending is swallowed (the accumulator never goes negative).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>refresh_drain_active</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>refresh_ctrl.sv:126</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = rem_nz/pend_nz   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1); holding the arbiter in the refresh branch requires BOTH quota and owed refreshes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>r_pending next-value</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>refresh_ctrl.sv:98-108</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>refresh_req_o (registered) = pending&gt;0. Saturation at 8 = a JEDEC retention violation looming — the arbiter must be serving REFs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>enable &amp;&amp; expired</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>w_grant_accept</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>min(pending+1, 8)  (postpone cap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>pending-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>pending (net zero)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>busy_o</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>pumice_mem_cmd_scheduler.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>busy = !init_done || refresh_req || w_cmd_rd_valid || (|w_bank_row_active[0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>rows = init_done/refresh_req   cols = cmd_rd_valid/any_row_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -2131,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3262,6 +3262,166 @@
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>moved into the scheduler 2026-07-22 (was a TB bind)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Refresh iface</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>refresh_req_i / refresh_drain_i</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>refresh_ctrl</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Owed-refresh request (pending&gt;0) and burst-drain hold.</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>req high =&gt; arbiter priority-2 branch; columns/ACTs starve by design while high</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Refresh iface</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>refresh_grant_o</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Pulsed when the REF command FIRES (w_fire_out &amp;&amp; r_grant).</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>one grant per issued REF; decrements pending + drain quota</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Timing cfg</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>t_rfc_i</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>CSR (TIMINGS_RFC_REFI.tRFC)</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Mission-mode REF-&gt;ACT/REF recovery, MC cycles (reset 16). Loaded into the arbiter's r_rfc_cnt on each fired REF.</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>no ACT or REF while r_rfc_cnt != 0 (w_rfc_busy) — audited by the history checker's positional tRFC check</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>added 2026-07-21: previously enforced by NOTHING in mission mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>DV hooks</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>CMD_HISTORY_EN / HIST_T_*</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>In-scheduler command-history scoreboard (audit-only shift registers on the ISSUED stream; $fatal assertions, sim-only).</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>default 0 = zero cost; -GCMD_HISTORY_EN=1 + --assert in DV</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>moved into the scheduler 2026-07-22 (was a TB bind)</t>
         </is>
@@ -3282,7 +3442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3547,40 +3707,40 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>rd_col_m[e]  (given rd_sch_valid_i[e])</t>
+          <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv (classify)</t>
+          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>rd_col_m = rhit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; twtr_ok &amp;&amp; rd_issue_ready &amp;&amp; !w_inflight_col</t>
+          <t>rd_col_m = rhit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; twtr_ok &amp;&amp; rd_issue_ready &amp;&amp; !w_inflight_col &amp;&amp; !w_rd_turn_block   [rd_issue_ready factored out as the enabling condition]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = rd_issue_ready/inflight_col</t>
+          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = inflight_col/rd_turn_block</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [rd_issue_ready=1, inflight_col=0], and there only the all-ones cell. A 1 on any other page = a column issued with the issue-FIFO full (double-issue) or tCCD overrun.</t>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [inflight_col=0, rd_turn_block=0], single all-ones cell. ANY 1 on an rd_turn_block=1 page = a RD issued into a write burst's DQ occupancy on the stale flopped twtr_ok — the 471/471 concurrent-soak corruption (issue #42).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>[rd_issue_ready=0, inflight_col=0]</t>
+          <t>[inflight_col=0, rd_turn_block=0]</t>
         </is>
       </c>
     </row>
@@ -3656,8 +3816,8 @@
       <c r="C38" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="21" t="n">
-        <v>0</v>
+      <c r="D38" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>0</v>
@@ -3685,7 +3845,7 @@
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>[rd_issue_ready=0, inflight_col=1]</t>
+          <t>[inflight_col=0, rd_turn_block=1]</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3950,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>[rd_issue_ready=1, inflight_col=0]</t>
+          <t>[inflight_col=1, rd_turn_block=0]</t>
         </is>
       </c>
     </row>
@@ -3866,8 +4026,8 @@
       <c r="C52" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="20" t="n">
-        <v>1</v>
+      <c r="D52" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="E52" s="21" t="n">
         <v>0</v>
@@ -3895,7 +4055,7 @@
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>[rd_issue_ready=1, inflight_col=1]</t>
+          <t>[inflight_col=1, rd_turn_block=1]</t>
         </is>
       </c>
     </row>
@@ -4000,40 +4160,40 @@
     <row r="63">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>wr_col_m[e]  (given wr_sch_valid_i[e])</t>
+          <t>wr_col_m[e]  (given wr_sch_valid_i[e] &amp;&amp; wr_commit_ready)</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv (classify)</t>
+          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>wr_col_m = whit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; trtw_ok &amp;&amp; wr_commit_ready &amp;&amp; !w_inflight_col</t>
+          <t>wr_col_m = whit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; trtw_ok &amp;&amp; wr_commit_ready &amp;&amp; !w_inflight_col &amp;&amp; !w_wr_turn_block   [wr_commit_ready factored out as the enabling condition]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = wr_commit_ready/inflight_col</t>
+          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = inflight_col/wr_turn_block</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Mirror of rd_col_m: single 1-cell on the [commit_ready=1, inflight_col=0] page only.</t>
+          <t>CHECK BY INSPECTION: Mirror of rd_col_m: 1s only on [inflight_col=0, wr_turn_block=0].</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>[wr_commit_ready=0, inflight_col=0]</t>
+          <t>[inflight_col=0, wr_turn_block=0]</t>
         </is>
       </c>
     </row>
@@ -4109,8 +4269,8 @@
       <c r="C72" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="21" t="n">
-        <v>0</v>
+      <c r="D72" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="E72" s="21" t="n">
         <v>0</v>
@@ -4138,7 +4298,7 @@
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>[wr_commit_ready=0, inflight_col=1]</t>
+          <t>[inflight_col=0, wr_turn_block=1]</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4403,7 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>[wr_commit_ready=1, inflight_col=0]</t>
+          <t>[inflight_col=1, wr_turn_block=0]</t>
         </is>
       </c>
     </row>
@@ -4319,8 +4479,8 @@
       <c r="C86" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="20" t="n">
-        <v>1</v>
+      <c r="D86" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="E86" s="21" t="n">
         <v>0</v>
@@ -4348,7 +4508,7 @@
     <row r="89">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>[wr_commit_ready=1, inflight_col=1]</t>
+          <t>[inflight_col=1, wr_turn_block=1]</t>
         </is>
       </c>
     </row>
@@ -4453,279 +4613,187 @@
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
+          <t>w_rd_turn_block / w_wr_turn_block</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
+          <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>act_m = !bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; bank_act_ready &amp;&amp; tfaw_ok &amp;&amp; trrd_ok &amp;&amp; !w_rfc_busy</t>
+          <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
+          <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="22" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=0]</t>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="19" t="inlineStr">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D103" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E103" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B103" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="19" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B104" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="21" t="n">
-        <v>0</v>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B105" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="21" t="n">
-        <v>0</v>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
+        </is>
+      </c>
+      <c r="D109" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>act_m = !bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; bank_act_ready &amp;&amp; tfaw_ok &amp;&amp; trrd_ok &amp;&amp; !w_rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B106" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="19" t="inlineStr">
+      <c r="E115" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B107" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="22" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="19" t="inlineStr">
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C110" s="19" t="inlineStr">
+      <c r="B116" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D110" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E110" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="19" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B111" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="19" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B112" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B113" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="22" t="inlineStr">
-        <is>
-          <t>[trrd_ok=1, rfc_busy=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="19" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D117" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E117" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="19" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B118" s="21" t="n">
@@ -4734,8 +4802,8 @@
       <c r="C118" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="20" t="n">
-        <v>1</v>
+      <c r="D118" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="21" t="n">
         <v>0</v>
@@ -4744,93 +4812,93 @@
     <row r="119">
       <c r="A119" s="19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B119" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="19" t="inlineStr">
+      <c r="D122" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B120" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="19" t="inlineStr">
+      <c r="E122" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B121" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="inlineStr">
-        <is>
-          <t>[trrd_ok=1, rfc_busy=1]</t>
-        </is>
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="19" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D124" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E124" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B124" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="19" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B125" s="21" t="n">
@@ -4849,90 +4917,131 @@
     <row r="126">
       <c r="A126" s="19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B126" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B126" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="19" t="inlineStr">
+      <c r="D129" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B127" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="E129" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B128" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="21" t="n">
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B130" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="15" t="inlineStr">
-        <is>
-          <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (classify)</t>
-        </is>
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="17" t="inlineStr">
-        <is>
-          <t>pre_m = bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; !hit &amp;&amp; bank_pre_ready</t>
-        </is>
+      <c r="A132" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B132" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>rows = row_active/guarded   cols = hit/pre_ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="18" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="22" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=1]</t>
         </is>
       </c>
     </row>
@@ -5024,8 +5133,8 @@
       <c r="B140" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C140" s="20" t="n">
-        <v>1</v>
+      <c r="C140" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="D140" s="21" t="n">
         <v>0</v>
@@ -5037,33 +5146,33 @@
     <row r="143">
       <c r="A143" s="15" t="inlineStr">
         <is>
-          <t>w_guarded[b]</t>
+          <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+          <t>pumice_cmd_arbiter.sv (classify)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [bank_match = r_bank==b]</t>
+          <t>pre_m = bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; !hit &amp;&amp; bank_pre_ready</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rows = guard0/guard1   cols = inflight_rowop_or_col/bank_match</t>
+          <t>rows = row_active/guarded   cols = hit/pre_ready</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
         </is>
       </c>
     </row>
@@ -5101,8 +5210,8 @@
       <c r="C149" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D149" s="20" t="n">
-        <v>1</v>
+      <c r="D149" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="E149" s="21" t="n">
         <v>0</v>
@@ -5114,17 +5223,17 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B150" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" s="20" t="n">
-        <v>1</v>
+      <c r="B150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -5133,17 +5242,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B151" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="20" t="n">
-        <v>1</v>
+      <c r="B151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5152,56 +5261,71 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B152" s="20" t="n">
-        <v>1</v>
+      <c r="B152" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="C152" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D152" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="20" t="n">
-        <v>1</v>
+      <c r="D152" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>w_out_ready / w_fire_out</t>
+          <t>w_guarded[b]</t>
         </is>
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv (output register)</t>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
         <is>
-          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [bank_match = r_bank==b]</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
+          <t>rows = guard0/guard1   cols = inflight_rowop_or_col/bank_match</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
+          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D160" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5211,8 +5335,17 @@
           <t>00</t>
         </is>
       </c>
-      <c r="B161" s="20" t="n">
+      <c r="B161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="20" t="n">
         <v>1</v>
+      </c>
+      <c r="E161" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -5224,6 +5357,15 @@
       <c r="B162" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="C162" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="19" t="inlineStr">
@@ -5234,6 +5376,15 @@
       <c r="B163" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="C163" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="19" t="inlineStr">
@@ -5244,274 +5395,363 @@
       <c r="B164" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="C164" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="15" t="inlineStr">
         <is>
+          <t>w_out_ready / w_fire_out</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (output register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="17" t="inlineStr">
+        <is>
+          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B173" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B175" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
           <t>pick priority (strict, first match wins)</t>
         </is>
       </c>
-      <c r="D167" s="16" t="inlineStr">
+      <c r="D179" s="16" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="18" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
         <is>
           <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="23" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="23" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B169" s="23" t="inlineStr">
+      <c r="B181" s="23" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C169" s="23" t="inlineStr">
+      <c r="C181" s="23" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="D169" s="23" t="inlineStr">
+      <c r="D181" s="23" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="24" t="n">
+    <row r="182">
+      <c r="A182" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B170" s="24" t="inlineStr">
+      <c r="B182" s="24" t="inlineStr">
         <is>
           <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
         </is>
       </c>
-      <c r="C170" s="24" t="inlineStr">
+      <c r="C182" s="24" t="inlineStr">
         <is>
           <t>forward init op</t>
         </is>
       </c>
-      <c r="D170" s="24" t="inlineStr">
+      <c r="D182" s="24" t="inlineStr">
         <is>
           <t>MRS/PRE/REF from init_sequencer verbatim</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="24" t="n">
+    <row r="183">
+      <c r="A183" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B171" s="24" t="inlineStr">
+      <c r="B183" s="24" t="inlineStr">
         <is>
           <t>refresh_req_i || refresh_drain_i</t>
         </is>
       </c>
-      <c r="C171" s="24" t="inlineStr">
+      <c r="C183" s="24" t="inlineStr">
         <is>
           <t>refresh branch</t>
         </is>
       </c>
-      <c r="D171" s="24" t="inlineStr">
+      <c r="D183" s="24" t="inlineStr">
         <is>
           <t>see refresh-branch K-map; never falls through while pending</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="24" t="n">
+    <row r="184">
+      <c r="A184" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B172" s="24" t="inlineStr">
+      <c r="B184" s="24" t="inlineStr">
         <is>
           <t>rd_col_f</t>
         </is>
       </c>
-      <c r="C172" s="24" t="inlineStr">
+      <c r="C184" s="24" t="inlineStr">
         <is>
           <t>RD/RDA row-hit</t>
         </is>
       </c>
-      <c r="D172" s="24" t="inlineStr">
+      <c r="D184" s="24" t="inlineStr">
         <is>
           <t>read priority over write</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="24" t="n">
+    <row r="185">
+      <c r="A185" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B173" s="24" t="inlineStr">
+      <c r="B185" s="24" t="inlineStr">
         <is>
           <t>wr_col_f</t>
         </is>
       </c>
-      <c r="C173" s="24" t="inlineStr">
+      <c r="C185" s="24" t="inlineStr">
         <is>
           <t>WR/WRA row-hit</t>
         </is>
       </c>
-      <c r="D173" s="24" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="24" t="n">
+      <c r="D185" s="24" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B174" s="24" t="inlineStr">
+      <c r="B186" s="24" t="inlineStr">
         <is>
           <t>rd_act_f</t>
         </is>
       </c>
-      <c r="C174" s="24" t="inlineStr">
+      <c r="C186" s="24" t="inlineStr">
         <is>
           <t>ACT for oldest pending read</t>
         </is>
       </c>
-      <c r="D174" s="24" t="inlineStr">
+      <c r="D186" s="24" t="inlineStr">
         <is>
           <t>bank-parallel</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="24" t="n">
+    <row r="187">
+      <c r="A187" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="B175" s="24" t="inlineStr">
+      <c r="B187" s="24" t="inlineStr">
         <is>
           <t>wr_act_f</t>
         </is>
       </c>
-      <c r="C175" s="24" t="inlineStr">
+      <c r="C187" s="24" t="inlineStr">
         <is>
           <t>ACT for oldest pending write</t>
         </is>
       </c>
-      <c r="D175" s="24" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="24" t="n">
+      <c r="D187" s="24" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="B176" s="24" t="inlineStr">
+      <c r="B188" s="24" t="inlineStr">
         <is>
           <t>rd_pre_f</t>
         </is>
       </c>
-      <c r="C176" s="24" t="inlineStr">
+      <c r="C188" s="24" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (read)</t>
         </is>
       </c>
-      <c r="D176" s="24" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="24" t="n">
+      <c r="D188" s="24" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="B177" s="24" t="inlineStr">
+      <c r="B189" s="24" t="inlineStr">
         <is>
           <t>wr_pre_f</t>
         </is>
       </c>
-      <c r="C177" s="24" t="inlineStr">
+      <c r="C189" s="24" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (write)</t>
         </is>
       </c>
-      <c r="D177" s="24" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="15" t="inlineStr">
+      <c r="D189" s="24" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="inlineStr">
         <is>
           <t>r_rfc_cnt next-value</t>
         </is>
       </c>
-      <c r="D180" s="16" t="inlineStr">
+      <c r="D192" s="16" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="18" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
         <is>
           <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="23" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="23" t="inlineStr">
         <is>
           <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
         </is>
       </c>
-      <c r="B182" s="23" t="inlineStr">
+      <c r="B194" s="23" t="inlineStr">
         <is>
           <t>r_rfc_cnt != 0</t>
         </is>
       </c>
-      <c r="C182" s="23" t="inlineStr">
+      <c r="C194" s="23" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="24" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B183" s="24" t="inlineStr">
+      <c r="B195" s="24" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C183" s="24" t="inlineStr">
+      <c r="C195" s="24" t="inlineStr">
         <is>
           <t>t_rfc_i (load)</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="24" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B184" s="24" t="inlineStr">
+      <c r="B196" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C184" s="24" t="inlineStr">
+      <c r="C196" s="24" t="inlineStr">
         <is>
           <t>r_rfc_cnt - 1</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="24" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B185" s="24" t="inlineStr">
+      <c r="B197" s="24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C185" s="24" t="inlineStr">
+      <c r="C197" s="24" t="inlineStr">
         <is>
           <t>0 (idle)</t>
         </is>

--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,9 +69,13 @@
     </font>
     <font>
       <i val="1"/>
+      <color rgb="00B45309"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +105,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +186,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -184,6 +196,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1115,7 +1133,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>IDEAL: B-gate keyed on the CAM entry's own agg/last, NOT on a per-bank single-outstanding flag -- so two same-bank writes in flight each retire independently (today's deadlock is here).</t>
+          <t>IDEAL: B-gate keyed on the CAM entry's own agg/last, NOT on a IDEAL: B-gate keyed on the CAM entry's own agg/last, NOT on a per-bank single-outstanding flag, so two same-bank writes in flight each retire independently. RTL STATUS 2026-09-10: IMPLEMENTED. commit_done_valid_o is strobed from the drain head's CARRIED agg/slast tag (w_cm_fire &amp;&amp; w_hd_blast &amp;&amp; (!w_hd_agg || w_hd_slast)); no per-bank outstanding flag exists in the write CAM at all. (pumice_wr_data_cam.sv:624-627)</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1398,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Today the arbiter allows exactly ONE column per bank in flight (occupancy mask) because the return/drain path deadlocks otherwise. IDEAL: a small per-bank counter permits up to RETURN_DEPTH columns; issue is gated by tCCD + counter&lt;DEPTH, never by pipeline occupancy.</t>
+          <t>RTL STATUS 2026-09-10: the one-column-per-bank restriction now applies ONLY to auto-precharge columns (the mask is AP-gated). Non-AP columns are gated by tCCD and the per-entry double-issue mask alone, which is what this row asked for. IDEAL for the AP case is still a small per-bank counter permitting up to RETURN_DEPTH columns rather than one.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1661,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Today the return is POSITIONAL: fill matches the issue-FIFO head (rd_cmd_cam), aligner slices fixed BL_WORDS with no per-read id. One short/lost burst desyncs every later read and wedges the AR-order drain forever. IDEAL: carry a read TAG end to end and length-check.</t>
+          <t>RTL STATUS 2026-09-10: PARTLY ADDRESSED, hazard STANDS. pumice_rd_return_ring now allocates a ticket per read at admit (AR order) and drains from the ring head, which decoupled CAM occupancy from the return. But the RETURN itself is still POSITIONAL: a returning beat lands in the issue_q HEAD's slot because DRAM carries no tag back, and there is still no length check, so a short or lost burst still desyncs every later read. IDEAL unchanged: carry a read TAG end to end and length-check. (pumice_rd_return_ring.sv:122-134)</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2692,2253 +2710,2359 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
           <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros. Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="18" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="C12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="B14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>refresh-branch action (given refresh_req_i||refresh_drain_i)</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (priority 2)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>if (any_active) { if (rfsh_pre_found) PRE else wait } else if (ref_safe) REF else wait</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>rows = any_active/rfsh_pre_found   cols = ref_safe</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="18" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B25" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C25" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C26" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C27" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C28" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>rd_col_m = rhit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; twtr_ok &amp;&amp; rd_issue_ready &amp;&amp; !w_inflight_col &amp;&amp; !w_rd_turn_block   [rd_issue_ready factored out as the enabling condition]</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = inflight_col/rd_turn_block</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the page [inflight_col=0, rd_turn_block=0], single all-ones cell. ANY 1 on an rd_turn_block=1 page = a RD issued into a write burst's DQ occupancy on the stale flopped twtr_ok — the 471/471 concurrent-soak corruption (issue #42).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=0, rd_turn_block=0]</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="18" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="B39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="B40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="19" t="n">
+      <c r="B41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="E41" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="B42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=0, rd_turn_block=1]</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="18" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="B46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="B47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="B48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="B49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=1, rd_turn_block=0]</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="18" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="B53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="B54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="B55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=1, rd_turn_block=1]</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="18" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B57" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="B60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="B61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="B62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="B63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>wr_col_m[e]  (given wr_sch_valid_i[e] &amp;&amp; wr_commit_ready)</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>wr_col_m = whit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; trtw_ok &amp;&amp; wr_commit_ready &amp;&amp; !w_inflight_col &amp;&amp; !w_wr_turn_block   [wr_commit_ready factored out as the enabling condition]</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = inflight_col/wr_turn_block</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Mirror of rd_col_m: 1s only on [inflight_col=0, wr_turn_block=0].</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>[inflight_col=0, wr_turn_block=0]</t>
-        </is>
-      </c>
-    </row>
     <row r="69">
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D69" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: Mirror of rd_col_m: 1s only on [inflight_col=0, wr_turn_block=0].</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>[inflight_col=0, wr_turn_block=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="19" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B70" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="D73" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B72" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="19" t="n">
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="E76" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="B77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=0, wr_turn_block=1]</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="18" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E80" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="18" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B77" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="18" t="inlineStr">
+      <c r="B81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="18" t="inlineStr">
+      <c r="B82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B79" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="18" t="inlineStr">
+      <c r="B83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B80" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="B84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=1, wr_turn_block=0]</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="18" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D83" s="18" t="inlineStr">
+      <c r="D87" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E83" s="18" t="inlineStr">
+      <c r="E87" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="18" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B84" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="B88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B85" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="B89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B86" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="18" t="inlineStr">
+      <c r="B90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="B91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>[inflight_col=1, wr_turn_block=1]</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="18" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C90" s="18" t="inlineStr">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D90" s="18" t="inlineStr">
+      <c r="D94" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E90" s="18" t="inlineStr">
+      <c r="E94" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="18" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="18" t="inlineStr">
+      <c r="B95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B92" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="18" t="inlineStr">
+      <c r="B96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B93" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="18" t="inlineStr">
+      <c r="B97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B94" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="13" t="inlineStr">
+      <c r="B98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="inlineStr">
         <is>
           <t>w_rd_turn_block / w_wr_turn_block</t>
         </is>
       </c>
-      <c r="D97" s="15" t="inlineStr">
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B103" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="104">
-      <c r="A104" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B104" s="19" t="n">
-        <v>1</v>
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="18" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B108" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B105" s="19" t="n">
+      <c r="B110" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B106" s="19" t="n">
+      <c r="B111" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="13" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
         <is>
           <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t>act_m = !bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; bank_act_ready &amp;&amp; tfaw_ok &amp;&amp; trrd_ok &amp;&amp; !w_rfc_busy</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D115" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E115" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="117">
-      <c r="A117" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B117" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="20" t="n">
-        <v>0</v>
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B118" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="18" t="inlineStr">
+      <c r="E121" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+    </row>
+    <row r="122">
+      <c r="A122" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B122" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B124" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>[trrd_ok=0, rfc_busy=1]</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="18" t="inlineStr">
+    <row r="128">
+      <c r="B128" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C122" s="18" t="inlineStr">
+      <c r="C128" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D122" s="18" t="inlineStr">
+      <c r="D128" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E122" s="18" t="inlineStr">
+      <c r="E128" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="18" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="18" t="inlineStr">
+      <c r="B129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B124" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="18" t="inlineStr">
+      <c r="B130" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="18" t="inlineStr">
+      <c r="B131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B126" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+      <c r="B132" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>[trrd_ok=1, rfc_busy=0]</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="18" t="inlineStr">
+    <row r="135">
+      <c r="B135" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C129" s="18" t="inlineStr">
+      <c r="C135" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D129" s="18" t="inlineStr">
+      <c r="D135" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E129" s="18" t="inlineStr">
+      <c r="E135" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="18" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="19" t="n">
+      <c r="B136" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E130" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="18" t="inlineStr">
+      <c r="E136" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="18" t="inlineStr">
+      <c r="B137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="18" t="inlineStr">
+      <c r="B138" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+      <c r="B139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>[trrd_ok=1, rfc_busy=1]</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="B136" s="18" t="inlineStr">
+    <row r="142">
+      <c r="B142" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C136" s="18" t="inlineStr">
+      <c r="C142" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D136" s="18" t="inlineStr">
+      <c r="D142" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E136" s="18" t="inlineStr">
+      <c r="E142" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="18" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="18" t="inlineStr">
+      <c r="B143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="18" t="inlineStr">
+      <c r="B144" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="18" t="inlineStr">
+      <c r="B145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="13" t="inlineStr">
+      <c r="B146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="inlineStr">
         <is>
           <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D143" s="15" t="inlineStr">
+      <c r="D149" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify)</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="16" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
         <is>
           <t>pre_m = bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; !hit &amp;&amp; bank_pre_ready</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = hit/pre_ready</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="17" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    hit =&gt; row_active. A row HIT is defined as 'this bank has a row open AND it is the requested one', so a hit with no open row is not a state the hardware can be in -- it is a contradiction in the term itself, not a case the logic happens to avoid.</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:562-565 (rhit/whit = r_bank_row_active[b] &amp;&amp; row==open_row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    pre_ready =&gt; row_active. safe_pre_o is ANDed with r_row_valid, so tRAS/tRTP/tWR clearance is only ever reported for a bank that has a row to precharge.</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:138 (safe_pre_o = r_row_valid &amp;&amp; (r_ras=='0) &amp;&amp; (r_preblk=='0) &amp;&amp; !r_ap_pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="B148" s="18" t="inlineStr">
+    <row r="157">
+      <c r="B157" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C148" s="18" t="inlineStr">
+      <c r="C157" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D148" s="18" t="inlineStr">
+      <c r="D157" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E148" s="18" t="inlineStr">
+      <c r="E157" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="18" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="18" t="inlineStr">
+      <c r="B158" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D158" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E158" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="18" t="inlineStr">
+      <c r="B159" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D159" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E159" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="18" t="inlineStr">
+      <c r="B160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" s="19" t="n">
+      <c r="B161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="13" t="inlineStr">
-        <is>
-          <t>w_guarded[b]</t>
-        </is>
-      </c>
-      <c r="D155" s="15" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (guard fold)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="inlineStr">
-        <is>
-          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [bank_match = r_bank==b]</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>rows = guard0/guard1   cols = inflight_rowop_or_col/bank_match</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C160" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D160" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E160" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B161" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B162" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C162" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" s="19" t="n">
-        <v>1</v>
+      <c r="D161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
+          <t>cells: 10 reachable, 6 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="inlineStr">
+        <is>
+          <t>w_guarded[b]</t>
+        </is>
+      </c>
+      <c r="D165" s="15" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [bank_match = r_bank==b]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>rows = guard0/guard1   cols = inflight_rowop_or_col/bank_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C171" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D171" s="19" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B163" s="19" t="n">
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B172" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C163" s="19" t="n">
+      <c r="E172" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B173" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D163" s="19" t="n">
+      <c r="C173" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="19" t="n">
+      <c r="D173" s="20" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="18" t="inlineStr">
+      <c r="E173" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B164" s="19" t="n">
+      <c r="B175" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C164" s="19" t="n">
+      <c r="C175" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D164" s="19" t="n">
+      <c r="D175" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E164" s="19" t="n">
+      <c r="E175" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="13" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
         <is>
           <t>w_out_ready / w_fire_out</t>
         </is>
       </c>
-      <c r="D167" s="15" t="inlineStr">
+      <c r="D178" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (output register)</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="16" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="16" t="inlineStr">
         <is>
           <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="17" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="B172" s="18" t="inlineStr">
+    <row r="184">
+      <c r="B184" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="18" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B173" s="19" t="n">
+      <c r="B185" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="18" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B174" s="19" t="n">
+      <c r="B186" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="18" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B175" s="19" t="n">
+      <c r="B187" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="18" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B176" s="19" t="n">
+      <c r="B188" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="13" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="13" t="inlineStr">
         <is>
           <t>pick priority (strict, first match wins)</t>
         </is>
       </c>
-      <c r="D179" s="15" t="inlineStr">
+      <c r="D191" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="17" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
         <is>
           <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="21" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="24" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B181" s="21" t="inlineStr">
+      <c r="B193" s="24" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C181" s="21" t="inlineStr">
+      <c r="C193" s="24" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="D181" s="21" t="inlineStr">
+      <c r="D193" s="24" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="22" t="n">
+    <row r="194">
+      <c r="A194" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B182" s="22" t="inlineStr">
+      <c r="B194" s="25" t="inlineStr">
         <is>
           <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
         </is>
       </c>
-      <c r="C182" s="22" t="inlineStr">
+      <c r="C194" s="25" t="inlineStr">
         <is>
           <t>forward init op</t>
         </is>
       </c>
-      <c r="D182" s="22" t="inlineStr">
+      <c r="D194" s="25" t="inlineStr">
         <is>
           <t>MRS/PRE/REF from init_sequencer verbatim</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="22" t="n">
+    <row r="195">
+      <c r="A195" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B183" s="22" t="inlineStr">
+      <c r="B195" s="25" t="inlineStr">
         <is>
           <t>refresh_req_i || refresh_drain_i</t>
         </is>
       </c>
-      <c r="C183" s="22" t="inlineStr">
+      <c r="C195" s="25" t="inlineStr">
         <is>
           <t>refresh branch</t>
         </is>
       </c>
-      <c r="D183" s="22" t="inlineStr">
+      <c r="D195" s="25" t="inlineStr">
         <is>
           <t>see refresh-branch K-map; never falls through while pending</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="22" t="n">
+    <row r="196">
+      <c r="A196" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B184" s="22" t="inlineStr">
+      <c r="B196" s="25" t="inlineStr">
         <is>
           <t>rd_col_f</t>
         </is>
       </c>
-      <c r="C184" s="22" t="inlineStr">
+      <c r="C196" s="25" t="inlineStr">
         <is>
           <t>RD/RDA row-hit</t>
         </is>
       </c>
-      <c r="D184" s="22" t="inlineStr">
+      <c r="D196" s="25" t="inlineStr">
         <is>
           <t>read priority over write</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="22" t="n">
+    <row r="197">
+      <c r="A197" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B185" s="22" t="inlineStr">
+      <c r="B197" s="25" t="inlineStr">
         <is>
           <t>wr_col_f</t>
         </is>
       </c>
-      <c r="C185" s="22" t="inlineStr">
+      <c r="C197" s="25" t="inlineStr">
         <is>
           <t>WR/WRA row-hit</t>
         </is>
       </c>
-      <c r="D185" s="22" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="22" t="n">
+      <c r="D197" s="25" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B186" s="22" t="inlineStr">
+      <c r="B198" s="25" t="inlineStr">
         <is>
           <t>rd_act_f</t>
         </is>
       </c>
-      <c r="C186" s="22" t="inlineStr">
+      <c r="C198" s="25" t="inlineStr">
         <is>
           <t>ACT for oldest pending read</t>
         </is>
       </c>
-      <c r="D186" s="22" t="inlineStr">
+      <c r="D198" s="25" t="inlineStr">
         <is>
           <t>bank-parallel</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="22" t="n">
+    <row r="199">
+      <c r="A199" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B187" s="22" t="inlineStr">
+      <c r="B199" s="25" t="inlineStr">
         <is>
           <t>wr_act_f</t>
         </is>
       </c>
-      <c r="C187" s="22" t="inlineStr">
+      <c r="C199" s="25" t="inlineStr">
         <is>
           <t>ACT for oldest pending write</t>
         </is>
       </c>
-      <c r="D187" s="22" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="22" t="n">
+      <c r="D199" s="25" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B188" s="22" t="inlineStr">
+      <c r="B200" s="25" t="inlineStr">
         <is>
           <t>rd_pre_f</t>
         </is>
       </c>
-      <c r="C188" s="22" t="inlineStr">
+      <c r="C200" s="25" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (read)</t>
         </is>
       </c>
-      <c r="D188" s="22" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="22" t="n">
+      <c r="D200" s="25" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B189" s="22" t="inlineStr">
+      <c r="B201" s="25" t="inlineStr">
         <is>
           <t>wr_pre_f</t>
         </is>
       </c>
-      <c r="C189" s="22" t="inlineStr">
+      <c r="C201" s="25" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (write)</t>
         </is>
       </c>
-      <c r="D189" s="22" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="13" t="inlineStr">
+      <c r="D201" s="25" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="13" t="inlineStr">
         <is>
           <t>r_rfc_cnt next-value</t>
         </is>
       </c>
-      <c r="D192" s="15" t="inlineStr">
+      <c r="D204" s="15" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="17" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
         <is>
           <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="21" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="24" t="inlineStr">
         <is>
           <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
         </is>
       </c>
-      <c r="B194" s="21" t="inlineStr">
+      <c r="B206" s="24" t="inlineStr">
         <is>
           <t>r_rfc_cnt != 0</t>
         </is>
       </c>
-      <c r="C194" s="21" t="inlineStr">
+      <c r="C206" s="24" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="22" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B195" s="22" t="inlineStr">
+      <c r="B207" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C195" s="22" t="inlineStr">
+      <c r="C207" s="25" t="inlineStr">
         <is>
           <t>t_rfc_i (load)</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="22" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B196" s="22" t="inlineStr">
+      <c r="B208" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C196" s="22" t="inlineStr">
+      <c r="C208" s="25" t="inlineStr">
         <is>
           <t>r_rfc_cnt - 1</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="22" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B197" s="22" t="inlineStr">
+      <c r="B209" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C197" s="22" t="inlineStr">
+      <c r="C209" s="25" t="inlineStr">
         <is>
           <t>0 (idle)</t>
         </is>
@@ -4955,7 +5079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5011,702 +5135,788 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (0,1,1): closed row, tRP and tRC elapsed. Any 1 with row_valid=1 would re-ACT an open bank.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="18" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="19" t="n">
+      <c r="B12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>safe_rd_o / safe_wr_o</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>bank_timer.sv:135-136</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>safe_rd = safe_wr = r_row_valid &amp;&amp; (r_rcd == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd==0   cols = ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). ap_pending=1 must kill columns — the row is committed to auto-close.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="18" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="B25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="C26" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="B27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>safe_pre_o</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>bank_timer.sv:138</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>safe_pre = r_row_valid &amp;&amp; (r_ras == 0) &amp;&amp; (r_preblk == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>rows = row_valid/ras==0   cols = preblk==0/ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="19" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="B40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>w_ap_fire (internal auto-precharge)</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>bank_timer.sv:88</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>w_ap_fire = r_ap_pending &amp;&amp; (r_preblk == 0) &amp;&amp; (r_ras == 0)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>rows = ap_pending/preblk==0   cols = ras==0</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="20" t="n">
-        <v>0</v>
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="B51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="19" t="n">
+      <c r="B52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="B53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>state_o (observability only)</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>bank_timer.sv:144-147</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>rv ? (rcd_nz ? ACTIVATING : ACTIVE) : (rp_nz ? PRECHARGING : IDLE)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd_nz   cols = rp_nz</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rcd_nz =&gt; row_valid. The ACT edge loads tRCD and sets row_valid together, and nothing else loads tRCD, so a bank counting tRCD always has its row marked open.</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:96 (set_act_i -&gt; r_rcd) + :116 (r_row_valid &lt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rp_nz =&gt; !row_valid. The PRE edge (explicit or auto) loads tRP and clears row_valid together.</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:106 (set_pre_i||w_ap_fire -&gt; r_rp) + :120-123 (r_row_valid &lt;= 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Therefore rcd_nz and rp_nz are MUTUALLY EXCLUSIVE -- a bank cannot be inside tRCD and tRP at once. That single relation removes a quarter of this grid; drawing 0s there would assert the decode had been checked in a state the timers forbid.</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:96,106,116,120-123</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="18" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n">
+      <c r="B66" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="19" t="n">
+      <c r="C66" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B59" s="19" t="n">
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="19" t="n">
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>cells: 4 reachable, 4 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>row_valid / ap_pending next-state priority</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>bank_timer.sv:115-127</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>Strict priority ACT &gt; PRE &gt; auto-PRE &gt; column. The arbiter never issues ACT and PRE to one bank in one cycle (single-issue), so rows 1-2 cannot conflict in practice.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="21" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="24" t="inlineStr">
         <is>
           <t>set_act</t>
         </is>
       </c>
-      <c r="B66" s="21" t="inlineStr">
+      <c r="B75" s="24" t="inlineStr">
         <is>
           <t>set_pre</t>
         </is>
       </c>
-      <c r="C66" s="21" t="inlineStr">
+      <c r="C75" s="24" t="inlineStr">
         <is>
           <t>w_ap_fire</t>
         </is>
       </c>
-      <c r="D66" s="21" t="inlineStr">
+      <c r="D75" s="24" t="inlineStr">
         <is>
           <t>set_rd||set_wr</t>
         </is>
       </c>
-      <c r="E66" s="21" t="inlineStr">
+      <c r="E75" s="24" t="inlineStr">
         <is>
           <t>row_valid'</t>
         </is>
       </c>
-      <c r="F66" s="21" t="inlineStr">
+      <c r="F75" s="24" t="inlineStr">
         <is>
           <t>ap_pending'</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="22" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B67" s="22" t="inlineStr">
+      <c r="B76" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="C76" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D76" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E67" s="22" t="inlineStr">
+      <c r="E76" s="25" t="inlineStr">
         <is>
           <t>1 (row=row_i)</t>
         </is>
       </c>
-      <c r="F67" s="22" t="inlineStr">
+      <c r="F76" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B77" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C77" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D77" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="E77" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F77" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="22" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B69" s="22" t="inlineStr">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C69" s="22" t="inlineStr">
+      <c r="C78" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D69" s="22" t="inlineStr">
+      <c r="D78" s="25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E69" s="22" t="inlineStr">
+      <c r="E78" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F69" s="22" t="inlineStr">
+      <c r="F78" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="22" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B70" s="22" t="inlineStr">
+      <c r="B79" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C79" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D79" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E70" s="22" t="inlineStr">
+      <c r="E79" s="25" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="F79" s="25" t="inlineStr">
         <is>
           <t>set_ap_i</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="22" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B71" s="22" t="inlineStr">
+      <c r="B80" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C71" s="22" t="inlineStr">
+      <c r="C80" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D71" s="22" t="inlineStr">
+      <c r="D80" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E71" s="22" t="inlineStr">
+      <c r="E80" s="25" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F71" s="22" t="inlineStr">
+      <c r="F80" s="25" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
@@ -7224,7 +7434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7280,369 +7490,390 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a grant with nothing pending is swallowed (the accumulator never goes negative).</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="18" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="B12" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B13" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B14" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>refresh_drain_active</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:126</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = rem_nz/pend_nz   cols = </t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1); holding the arbiter in the refresh branch requires BOTH quota and owed refreshes.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="18" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B24" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="B25" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="B27" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>r_pending next-value</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:98-108</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>refresh_req_o (registered) = pending&gt;0. Saturation at 8 = a JEDEC retention violation looming — the arbiter must be serving REFs.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>enable &amp;&amp; expired</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>w_grant_accept</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>min(pending+1, 8)  (postpone cap)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>pending-1</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>pending (net zero)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C36" s="25" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>busy_o</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>pumice_mem_cmd_scheduler.sv</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>busy = !init_done || refresh_req || w_cmd_rd_valid || (|w_bank_row_active[0])</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>rows = init_done/refresh_req   cols = cmd_rd_valid/any_row_active</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="19" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n">
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="19" t="n">
+      <c r="C46" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="19" t="n">
+      <c r="D46" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="19" t="n">
+      <c r="E46" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B44" s="19" t="n">
+      <c r="B47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="19" t="n">
+      <c r="C47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="D47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="19" t="n">
+      <c r="E47" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n">
+      <c r="B48" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="19" t="n">
+      <c r="C48" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="19" t="n">
+      <c r="D48" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="19" t="n">
+      <c r="E48" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="19" t="n">
+      <c r="B49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="19" t="n">
+      <c r="D49" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="19" t="n">
+      <c r="E49" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9819,7 +10050,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Broken today: the arbiter ANDs an extra !w_col_inflight_bank term (pick-pipeline occupancy) into rows 3/6/8, forcing one same-bank column per ~pipeline-depth instead of per tCCD. IDEAL removes it: only the DRAM timers above gate issue.</t>
+          <t>RTL STATUS 2026-09-10: LARGELY CLOSED. The arbiter used to AND a blanket !w_col_inflight_bank (pick-pipeline occupancy) into rows 3/6/8, forcing one same-bank column per ~pipeline-depth instead of per tCCD. It is now AP-GATED -- !(f_ap(b) &amp;&amp; w_col_inflight_bank[b]) -- so a non-AP column is gated only by the DRAM timers above, as this table asks. Narrowed rather than removed on purpose: an AP column closes the row behind it, and a second same-bank column picked against the stale open-row image would be issued to a closing row. Remaining gap: AP columns are still one-per-bank in flight. (pumice_cmd_arbiter.sv:589,605)</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10753,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Signals already present to build the overlay: r_bank (in-flight bank), w_inflight_col, w_inflight_preact, w_col_inflight_guard, r_ap_closing. Keep the per-ENTRY double-issue mask (w_rd/wr_col_inflight_ent); REMOVE the per-BANK occupancy mask (w_col_inflight_bank). See design/README.md + waves/07,08,09.</t>
+          <t>Signals already present to build the overlay: r_bank (in-flight bank), w_inflight_col, w_inflight_preact, w_col_inflight_guard, r_ap_closing. Keep the per-ENTRY double-issue mask Signals already present to build the overlay: r_bank (in-flight bank), w_inflight_col, w_inflight_preact, w_col_inflight_guard, r_ap_closing. Keep the per-ENTRY double-issue mask (w_rd/wr_col_inflight_ent). RTL STATUS 2026-09-10: the per-BANK occupancy mask was NOT removed as this line originally demanded -- it was AP-gated, which is the better answer. It guards a real stale-image hazard (r_ap_closing bridges the window the pipeline span alone cannot), so removing it outright would reopen that hole. Non-AP columns now see no per-bank restriction.</t>
         </is>
       </c>
     </row>

--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -2726,7 +2726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2775,14 +2775,14 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>w_ref_safe = !w_any_active &amp;&amp; !w_inflight_preact &amp;&amp; (r_guard0=='0) &amp;&amp; (r_guard1=='0) &amp;&amp; !w_rfc_busy   [guards collapsed: guards_nz = |r_guard0 | |r_guard1]</t>
+          <t>w_ref_safe = !w_any_active &amp;&amp; !w_inflight_preact &amp;&amp; (r_guard0=='0) &amp;&amp; (r_guard1=='0) &amp;&amp; !w_rfc_busy &amp;&amp; !r_grant   [guards collapsed: guards_nz = |r_guard0 | |r_guard1]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rows = any_active/inflight_preact   cols = guards_nz/rfc_busy</t>
+          <t>rows = any_active/inflight_preact   cols = guards_nz/rfc_busy   pages = grant</t>
         </is>
       </c>
     </row>
@@ -2796,59 +2796,47 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros. Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
+          <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros (on the grant=0 page; the grant=1 page is all-zero because a REF already granted this cycle must not re-arm). Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="21" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>[grant=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>0</v>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>0</v>
@@ -2863,7 +2851,7 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B14" s="23" t="n">
@@ -2882,323 +2870,323 @@
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="23" t="n">
+      <c r="B16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>[grant=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>refresh-branch action (given refresh_req_i||refresh_drain_i)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (priority 2)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>if (any_active) { if (rfsh_pre_found) PRE else wait } else if (ref_safe) REF else wait</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>rows = any_active/rfsh_pre_found   cols = ref_safe</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="21" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B33" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C33" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C34" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B35" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C35" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C36" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>rd_col_m = rhit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; twtr_ok &amp;&amp; rd_issue_ready &amp;&amp; !w_inflight_col &amp;&amp; !w_rd_turn_block   [rd_issue_ready factored out as the enabling condition]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = inflight_col/rd_turn_block</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>rd_col_m[e] = rhit &amp;&amp; r_bank_rdwr_ready[rb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; twtr_ok_i &amp;&amp; rd_issue_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [rd_issue_ready_i factored out as the enabling condition; dbl_issue = (f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]; col_guard = r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = dbl_issue/col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [inflight_col=0, rd_turn_block=0], single all-ones cell. ANY 1 on an rd_turn_block=1 page = a RD issued into a write burst's DQ occupancy on the stale flopped twtr_ok — the 471/471 concurrent-soak corruption (issue #42).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=0, rd_turn_block=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="21" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [dbl_issue=0, col_guard=0], single all-ones cell. A 1 anywhere on a col_guard=1 page would mean a RD issued through a turnaround/AP/precharge guard -- the class that produced the 471/471 concurrent-soak corruption (a RD into a write burst's DQ occupancy on a stale flopped twtr_ok).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E46" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=0, rd_turn_block=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B47" s="23" t="n">
@@ -3217,7 +3205,7 @@
     <row r="48">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B48" s="23" t="n">
@@ -3236,74 +3224,74 @@
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=1, rd_turn_block=0]</t>
-        </is>
+      <c r="B50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="21" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
+      <c r="C53" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D52" s="21" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="E53" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B54" s="23" t="n">
@@ -3322,7 +3310,7 @@
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B55" s="23" t="n">
@@ -3341,74 +3329,74 @@
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=1, rd_turn_block=1]</t>
-        </is>
+      <c r="B57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="21" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=1, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C59" s="21" t="inlineStr">
+      <c r="C60" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D59" s="21" t="inlineStr">
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E59" s="21" t="inlineStr">
+      <c r="E60" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B60" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B61" s="23" t="n">
@@ -3427,7 +3415,7 @@
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B62" s="23" t="n">
@@ -3446,219 +3434,219 @@
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B63" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="23" t="n">
+      <c r="B64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=1, col_guard=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E67" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B70" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
         <is>
           <t>wr_col_m[e]  (given wr_sch_valid_i[e] &amp;&amp; wr_commit_ready)</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="18" t="inlineStr">
-        <is>
-          <t>wr_col_m = whit &amp;&amp; bank_rdwr_ready &amp;&amp; tccd_ok &amp;&amp; trtw_ok &amp;&amp; wr_commit_ready &amp;&amp; !w_inflight_col &amp;&amp; !w_wr_turn_block   [wr_commit_ready factored out as the enabling condition]</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = inflight_col/wr_turn_block</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="19" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>wr_col_m[e] = whit &amp;&amp; r_bank_rdwr_ready[wb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; trtw_ok_i &amp;&amp; wr_commit_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [wr_commit_ready_i factored out; dbl_issue = (f_ap(wb) &amp;&amp; w_col_inflight_bank[wb]) | w_wr_col_inflight_ent[e]; col_guard = r_ap_closing[wb] | w_ref_col_block[wb] | w_wr_turn_block | w_ap_col_guard[wb] | w_pre_col_guard[wb] | w_preact_bank_guard[wb]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = dbl_issue/col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Mirror of rd_col_m: 1s only on [inflight_col=0, wr_turn_block=0].</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=0, wr_turn_block=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="21" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Exact mirror of rd_col_m with the write-side turnaround (trtw) and commit-ready: 1s only on [dbl_issue=0, col_guard=0].</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C73" s="21" t="inlineStr">
+      <c r="C81" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D73" s="21" t="inlineStr">
+      <c r="D81" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E73" s="21" t="inlineStr">
+      <c r="E81" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B74" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B77" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=0, wr_turn_block=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B81" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B82" s="23" t="n">
@@ -3677,7 +3665,7 @@
     <row r="83">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B83" s="23" t="n">
@@ -3696,74 +3684,74 @@
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=1, wr_turn_block=0]</t>
-        </is>
+      <c r="B85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="21" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C87" s="21" t="inlineStr">
+      <c r="C88" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D87" s="21" t="inlineStr">
+      <c r="D88" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E87" s="21" t="inlineStr">
+      <c r="E88" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B89" s="23" t="n">
@@ -3782,7 +3770,7 @@
     <row r="90">
       <c r="A90" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B90" s="23" t="n">
@@ -3801,74 +3789,74 @@
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B91" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>[inflight_col=1, wr_turn_block=1]</t>
-        </is>
+      <c r="B92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="21" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=1, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C94" s="21" t="inlineStr">
+      <c r="C95" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D94" s="21" t="inlineStr">
+      <c r="D95" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E94" s="21" t="inlineStr">
+      <c r="E95" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B95" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B96" s="23" t="n">
@@ -3887,7 +3875,7 @@
     <row r="97">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B97" s="23" t="n">
@@ -3906,306 +3894,306 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B98" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="23" t="n">
+      <c r="B99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=1, col_guard=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C102" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E102" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
         <is>
           <t>w_rd_turn_block / w_wr_turn_block</t>
         </is>
       </c>
-      <c r="D101" s="17" t="inlineStr">
+      <c r="D109" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="18" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
         <is>
           <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="19" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="19" t="inlineStr">
         <is>
           <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="21" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="21" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B108" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="21" t="inlineStr">
+      <c r="B116" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B109" s="22" t="n">
+      <c r="B117" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="21" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B110" s="22" t="n">
+      <c r="B118" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="21" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B111" s="22" t="n">
+      <c r="B119" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="15" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
         <is>
           <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D114" s="17" t="inlineStr">
+      <c r="D122" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
-        <is>
-          <t>act_m = !bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; bank_act_ready &amp;&amp; tfaw_ok &amp;&amp; trrd_ok &amp;&amp; !w_rfc_busy</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; tfaw_ok_i &amp;&amp; trrd_ok_i &amp;&amp; !w_rfc_busy   [wr_act_m[e] is the same with wb for rb]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="19" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=0, rfc_busy=0]</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" s="21" t="inlineStr">
+    <row r="129">
+      <c r="B129" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C121" s="21" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D121" s="21" t="inlineStr">
+      <c r="D129" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E121" s="21" t="inlineStr">
+      <c r="E129" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D128" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E128" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B130" s="23" t="n">
@@ -4224,7 +4212,7 @@
     <row r="131">
       <c r="A131" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B131" s="23" t="n">
@@ -4243,74 +4231,74 @@
     <row r="132">
       <c r="A132" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=1, rfc_busy=0]</t>
-        </is>
+      <c r="B133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="21" t="inlineStr">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C135" s="21" t="inlineStr">
+      <c r="C136" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D135" s="21" t="inlineStr">
+      <c r="D136" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E135" s="21" t="inlineStr">
+      <c r="E136" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B136" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B137" s="23" t="n">
@@ -4329,7 +4317,7 @@
     <row r="138">
       <c r="A138" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B138" s="23" t="n">
@@ -4348,74 +4336,74 @@
     <row r="139">
       <c r="A139" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=1, rfc_busy=1]</t>
-        </is>
+      <c r="B140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="B142" s="21" t="inlineStr">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C142" s="21" t="inlineStr">
+      <c r="C143" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D142" s="21" t="inlineStr">
+      <c r="D143" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E142" s="21" t="inlineStr">
+      <c r="E143" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B143" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B144" s="23" t="n">
@@ -4424,8 +4412,8 @@
       <c r="C144" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D144" s="23" t="n">
-        <v>0</v>
+      <c r="D144" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="E144" s="23" t="n">
         <v>0</v>
@@ -4434,7 +4422,7 @@
     <row r="145">
       <c r="A145" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B145" s="23" t="n">
@@ -4453,695 +4441,931 @@
     <row r="146">
       <c r="A146" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B146" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B146" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="23" t="n">
+      <c r="B147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="15" t="inlineStr">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C150" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D150" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E150" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B153" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="inlineStr">
         <is>
           <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D149" s="17" t="inlineStr">
+      <c r="D157" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify)</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="18" t="inlineStr">
-        <is>
-          <t>pre_m = bank_row_active &amp;&amp; !w_guarded[bank] &amp;&amp; !hit &amp;&amp; bank_pre_ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>rd_pre_m[e] = r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; !rhit &amp;&amp; r_bank_pre_ready[rb]   [wr_pre_m[e] is the same with wb/whit]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = hit/pre_ready</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="24" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="24" t="inlineStr">
         <is>
           <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="16" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    hit =&gt; row_active. A row HIT is defined as 'this bank has a row open AND it is the requested one', so a hit with no open row is not a state the hardware can be in -- it is a contradiction in the term itself, not a case the logic happens to avoid.</t>
         </is>
       </c>
-      <c r="D153" s="17" t="inlineStr">
+      <c r="D161" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:562-565 (rhit/whit = r_bank_row_active[b] &amp;&amp; row==open_row)</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="16" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    pre_ready =&gt; row_active. safe_pre_o is ANDed with r_row_valid, so tRAS/tRTP/tWR clearance is only ever reported for a bank that has a row to precharge.</t>
         </is>
       </c>
-      <c r="D154" s="17" t="inlineStr">
+      <c r="D162" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:138 (safe_pre_o = r_row_valid &amp;&amp; (r_ras=='0) &amp;&amp; (r_preblk=='0) &amp;&amp; !r_ap_pending)</t>
         </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C157" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D157" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E157" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B158" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D158" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E158" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B159" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D159" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E159" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B160" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B161" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D161" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C165" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D165" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E165" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B166" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D166" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E166" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B167" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D167" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E167" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B168" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B169" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20" t="inlineStr">
+        <is>
           <t>cells: 10 reachable, 6 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="15" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="15" t="inlineStr">
         <is>
           <t>w_guarded[b]</t>
         </is>
       </c>
-      <c r="D165" s="17" t="inlineStr">
+      <c r="D173" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="18" t="inlineStr">
-        <is>
-          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [bank_match = r_bank==b]</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>rows = guard0/guard1   cols = inflight_rowop_or_col/bank_match</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="19" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = r_bank==b]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>rows = guard0/guard1   cols = pick_guards_nz/inflight_rowop_or_col   pages = bank_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="inlineStr">
         <is>
           <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="20" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="B171" s="21" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>[bank_match=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C171" s="21" t="inlineStr">
+      <c r="C180" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D171" s="21" t="inlineStr">
+      <c r="D180" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E171" s="21" t="inlineStr">
+      <c r="E180" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="21" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B172" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="22" t="n">
+      <c r="B181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="21" t="inlineStr">
+      <c r="E181" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B173" s="22" t="n">
+      <c r="B182" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C173" s="22" t="n">
+      <c r="C182" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D173" s="22" t="n">
+      <c r="D182" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="22" t="n">
+      <c r="E182" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="21" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B174" s="22" t="n">
+      <c r="B183" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C174" s="22" t="n">
+      <c r="C183" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D174" s="22" t="n">
+      <c r="D183" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E174" s="22" t="n">
+      <c r="E183" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="21" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B175" s="22" t="n">
+      <c r="B184" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C175" s="22" t="n">
+      <c r="C184" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D175" s="22" t="n">
+      <c r="D184" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="22" t="n">
+      <c r="E184" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="15" t="inlineStr">
-        <is>
-          <t>w_out_ready / w_fire_out</t>
-        </is>
-      </c>
-      <c r="D178" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (output register)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="18" t="inlineStr">
-        <is>
-          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="B184" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="21" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>[bank_match=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B185" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="21" t="inlineStr">
+      <c r="C187" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B186" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="21" t="inlineStr">
+      <c r="D187" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B187" s="22" t="n">
-        <v>1</v>
+      <c r="E187" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="21" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B189" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B190" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B188" s="22" t="n">
+      <c r="B191" s="22" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="15" t="inlineStr">
+      <c r="C191" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>w_out_ready / w_fire_out</t>
+        </is>
+      </c>
+      <c r="D194" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (output register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="inlineStr">
+        <is>
+          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B201" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B202" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B203" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B204" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="inlineStr">
         <is>
           <t>pick priority (strict, first match wins)</t>
         </is>
       </c>
-      <c r="D191" s="17" t="inlineStr">
+      <c r="D207" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="20" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="20" t="inlineStr">
         <is>
           <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="26" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="26" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B193" s="26" t="inlineStr">
+      <c r="B209" s="26" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C193" s="26" t="inlineStr">
+      <c r="C209" s="26" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="D193" s="26" t="inlineStr">
+      <c r="D209" s="26" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="27" t="n">
+    <row r="210">
+      <c r="A210" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B194" s="27" t="inlineStr">
+      <c r="B210" s="27" t="inlineStr">
         <is>
           <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
         </is>
       </c>
-      <c r="C194" s="27" t="inlineStr">
+      <c r="C210" s="27" t="inlineStr">
         <is>
           <t>forward init op</t>
         </is>
       </c>
-      <c r="D194" s="27" t="inlineStr">
+      <c r="D210" s="27" t="inlineStr">
         <is>
           <t>MRS/PRE/REF from init_sequencer verbatim</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="27" t="n">
+    <row r="211">
+      <c r="A211" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B195" s="27" t="inlineStr">
+      <c r="B211" s="27" t="inlineStr">
         <is>
           <t>refresh_req_i || refresh_drain_i</t>
         </is>
       </c>
-      <c r="C195" s="27" t="inlineStr">
+      <c r="C211" s="27" t="inlineStr">
         <is>
           <t>refresh branch</t>
         </is>
       </c>
-      <c r="D195" s="27" t="inlineStr">
+      <c r="D211" s="27" t="inlineStr">
         <is>
           <t>see refresh-branch K-map; never falls through while pending</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="27" t="n">
+    <row r="212">
+      <c r="A212" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B196" s="27" t="inlineStr">
+      <c r="B212" s="27" t="inlineStr">
         <is>
           <t>rd_col_f</t>
         </is>
       </c>
-      <c r="C196" s="27" t="inlineStr">
+      <c r="C212" s="27" t="inlineStr">
         <is>
           <t>RD/RDA row-hit</t>
         </is>
       </c>
-      <c r="D196" s="27" t="inlineStr">
+      <c r="D212" s="27" t="inlineStr">
         <is>
           <t>read priority over write</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="27" t="n">
+    <row r="213">
+      <c r="A213" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B197" s="27" t="inlineStr">
+      <c r="B213" s="27" t="inlineStr">
         <is>
           <t>wr_col_f</t>
         </is>
       </c>
-      <c r="C197" s="27" t="inlineStr">
+      <c r="C213" s="27" t="inlineStr">
         <is>
           <t>WR/WRA row-hit</t>
         </is>
       </c>
-      <c r="D197" s="27" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="27" t="n">
+      <c r="D213" s="27" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B198" s="27" t="inlineStr">
+      <c r="B214" s="27" t="inlineStr">
         <is>
           <t>rd_act_f</t>
         </is>
       </c>
-      <c r="C198" s="27" t="inlineStr">
+      <c r="C214" s="27" t="inlineStr">
         <is>
           <t>ACT for oldest pending read</t>
         </is>
       </c>
-      <c r="D198" s="27" t="inlineStr">
+      <c r="D214" s="27" t="inlineStr">
         <is>
           <t>bank-parallel</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="27" t="n">
+    <row r="215">
+      <c r="A215" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B199" s="27" t="inlineStr">
+      <c r="B215" s="27" t="inlineStr">
         <is>
           <t>wr_act_f</t>
         </is>
       </c>
-      <c r="C199" s="27" t="inlineStr">
+      <c r="C215" s="27" t="inlineStr">
         <is>
           <t>ACT for oldest pending write</t>
         </is>
       </c>
-      <c r="D199" s="27" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="27" t="n">
+      <c r="D215" s="27" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B200" s="27" t="inlineStr">
+      <c r="B216" s="27" t="inlineStr">
         <is>
           <t>rd_pre_f</t>
         </is>
       </c>
-      <c r="C200" s="27" t="inlineStr">
+      <c r="C216" s="27" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (read)</t>
         </is>
       </c>
-      <c r="D200" s="27" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="27" t="n">
+      <c r="D216" s="27" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B201" s="27" t="inlineStr">
+      <c r="B217" s="27" t="inlineStr">
         <is>
           <t>wr_pre_f</t>
         </is>
       </c>
-      <c r="C201" s="27" t="inlineStr">
+      <c r="C217" s="27" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (write)</t>
         </is>
       </c>
-      <c r="D201" s="27" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="15" t="inlineStr">
+      <c r="D217" s="27" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
         <is>
           <t>r_rfc_cnt next-value</t>
         </is>
       </c>
-      <c r="D204" s="17" t="inlineStr">
+      <c r="D220" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="20" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="20" t="inlineStr">
         <is>
           <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="26" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="26" t="inlineStr">
         <is>
           <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
         </is>
       </c>
-      <c r="B206" s="26" t="inlineStr">
+      <c r="B222" s="26" t="inlineStr">
         <is>
           <t>r_rfc_cnt != 0</t>
         </is>
       </c>
-      <c r="C206" s="26" t="inlineStr">
+      <c r="C222" s="26" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="27" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B207" s="27" t="inlineStr">
+      <c r="B223" s="27" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C207" s="27" t="inlineStr">
+      <c r="C223" s="27" t="inlineStr">
         <is>
           <t>t_rfc_i (load)</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="27" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B208" s="27" t="inlineStr">
+      <c r="B224" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C208" s="27" t="inlineStr">
+      <c r="C224" s="27" t="inlineStr">
         <is>
           <t>r_rfc_cnt - 1</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="27" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B209" s="27" t="inlineStr">
+      <c r="B225" s="27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C209" s="27" t="inlineStr">
+      <c r="C225" s="27" t="inlineStr">
         <is>
           <t>0 (idle)</t>
         </is>
@@ -7642,14 +7866,14 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0)</t>
+          <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0) &amp;&amp; refresh_req_o</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = rem_nz/pend_nz   cols = </t>
+          <t>rows = rem_nz/pend_nz   cols = req_o</t>
         </is>
       </c>
     </row>
@@ -7663,14 +7887,19 @@
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1); holding the arbiter in the refresh branch requires BOTH quota and owed refreshes.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): holding the arbiter in the refresh branch requires quota AND owed refreshes AND the REGISTERED request. The req_o term is not redundant -- a postponed backlog withholds req_o while pending is non-zero, and without this term the drain window would open anyway and defeat the postpone credit.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7683,6 +7912,9 @@
       <c r="B24" s="23" t="n">
         <v>0</v>
       </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
@@ -7693,6 +7925,9 @@
       <c r="B25" s="23" t="n">
         <v>0</v>
       </c>
+      <c r="C25" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -7700,7 +7935,10 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7711,6 +7949,9 @@
         </is>
       </c>
       <c r="B27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="23" t="n">
         <v>0</v>
       </c>
     </row>

--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,10 +70,6 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00B45309"/>
     </font>
     <font>
       <i val="1"/>
@@ -149,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,10 +189,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,10 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2726,7 +2719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2787,128 +2780,127 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    any_active</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>|r_bank_row_active[RK0]</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    inflight_preact</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>r_pick_valid &amp;&amp; (r_do_act || r_do_pre)</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:302</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    guards_nz</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>(r_guard0 != '0) || (r_guard1 != '0)</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard stages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rfc_busy</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>w_rfc_busy -- r_rfc_cnt != 0, reloaded on each fired REF</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    grant</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>r_grant -- a REF was granted this cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) guards_nz and inflight_preact overlap in meaning but not in value: a pick in flight sets a guard only from the NEXT cycle, so all four combinations occur.</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (r_guard0/1 are registered off the pick)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros (on the grant=0 page; the grant=1 page is all-zero because a REF already granted this cycle must not re-arm). Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>[grant=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>[grant=1]</t>
+          <t>[grant=0]</t>
         </is>
       </c>
     </row>
@@ -2940,8 +2932,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
-        <v>0</v>
+      <c r="B20" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>0</v>
@@ -3010,614 +3002,624 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>[grant=1]</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    !any_active &amp; !inflight_preact &amp; !guards_nz &amp; !rfc_busy &amp; !grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>refresh-branch action (given refresh_req_i||refresh_drain_i)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (priority 2)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>if (any_active) { if (rfsh_pre_found) PRE else wait } else if (ref_safe) REF else wait</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>rows = any_active/rfsh_pre_found   cols = ref_safe</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    any_active</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>|r_bank_row_active[RK0]</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rfsh_pre_found</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>any j with r_bank_row_active[j] &amp;&amp; r_bank_pre_ready[j] &amp;&amp; !w_guarded[j]</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:1054-1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ref_safe</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>w_ref_safe -- see its own map above</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (refresh pick gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ref_safe =&gt; !any_active. w_ref_safe is literally ANDed with !w_any_active, so the two cannot both be 1 -- half this grid cannot occur.</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (w_ref_safe = !w_any_active &amp;&amp; ...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rfsh_pre_found =&gt; any_active. The search only sets it for a bank with r_bank_row_active[j] high, so 'a bank to precharge exists' implies 'a row is open'.</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:1054-1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="21" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>rd_col_m[e] = rhit &amp;&amp; r_bank_rdwr_ready[rb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; twtr_ok_i &amp;&amp; rd_issue_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [rd_issue_ready_i factored out as the enabling condition; dbl_issue = (f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]; col_guard = r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = dbl_issue/col_guard</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [dbl_issue=0, col_guard=0], single all-ones cell. A 1 anywhere on a col_guard=1 page would mean a RD issued through a turnaround/AP/precharge guard -- the class that produced the 471/471 concurrent-soak corruption (a RD into a write burst's DQ occupancy on a stale flopped twtr_ok).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>[dbl_issue=0, col_guard=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="22" t="n">
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="23" t="n">
-        <v>0</v>
+      <c r="C49" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>[dbl_issue=0, col_guard=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B52" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>cells: 4 reachable, 4 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>rd_col_m[e] = rhit &amp;&amp; r_bank_rdwr_ready[rb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; twtr_ok_i &amp;&amp; rd_issue_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [rd_issue_ready_i factored out as the enabling condition; dbl_issue = (f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]; col_guard = r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = dbl_issue/col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rhit</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>r_bank_row_active[RK0][rb] &amp;&amp; (row == r_bank_open_row[RK0][rb])</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:562-563</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rdwr_ready</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>r_bank_rdwr_ready[RK0][rb] = safe_rd_o = r_row_valid &amp;&amp; (r_rcd=='0) &amp;&amp; !r_ap_pending</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:135</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tccd_ok</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>w_tccd_fwd_ok -- FORWARD tCCD at classify time, not the flopped tccd_ok_i</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:420-432</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    twtr_ok</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>twtr_ok_i -- write-to-read turnaround, from global_timers</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>global_timers.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    dbl_issue</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>(f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:361-371,383-385</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    col_guard</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:574-580</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) rhit and rdwr_ready both require an open row but neither implies the other: a hit can be pending tRCD (rdwr_ready=0), and a ready bank can hold the WRONG row (rhit=0). All four occur.</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:562-565 + bank_timer.sv:135</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [dbl_issue=0, col_guard=0], single all-ones cell. A 1 anywhere on a col_guard=1 page would mean a RD issued through a turnaround/AP/precharge guard -- the class that produced the 471/471 concurrent-soak corruption (a RD into a write burst's DQ occupancy on a stale flopped twtr_ok).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C74" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D53" s="21" t="inlineStr">
+      <c r="D74" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E74" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="21" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B54" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="B75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="B76" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="B77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>[dbl_issue=1, col_guard=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E60" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B61" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B63" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>[dbl_issue=1, col_guard=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C67" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D67" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E67" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B69" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B71" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="15" t="inlineStr">
-        <is>
-          <t>wr_col_m[e]  (given wr_sch_valid_i[e] &amp;&amp; wr_commit_ready)</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>wr_col_m[e] = whit &amp;&amp; r_bank_rdwr_ready[wb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; trtw_ok_i &amp;&amp; wr_commit_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [wr_commit_ready_i factored out; dbl_issue = (f_ap(wb) &amp;&amp; w_col_inflight_bank[wb]) | w_wr_col_inflight_ent[e]; col_guard = r_ap_closing[wb] | w_ref_col_block[wb] | w_wr_turn_block | w_ap_col_guard[wb] | w_pre_col_guard[wb] | w_preact_bank_guard[wb]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = dbl_issue/col_guard</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Exact mirror of rd_col_m with the write-side turnaround (trtw) and commit-ready: 1s only on [dbl_issue=0, col_guard=0].</t>
-        </is>
+      <c r="B78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>[dbl_issue=0, col_guard=0]</t>
+          <t>[dbl_issue=0, col_guard=1]</t>
         </is>
       </c>
     </row>
@@ -3693,8 +3695,8 @@
       <c r="C84" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="22" t="n">
-        <v>1</v>
+      <c r="D84" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="E84" s="23" t="n">
         <v>0</v>
@@ -3722,7 +3724,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>[dbl_issue=0, col_guard=1]</t>
+          <t>[dbl_issue=1, col_guard=0]</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3829,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>[dbl_issue=1, col_guard=0]</t>
+          <t>[dbl_issue=1, col_guard=1]</t>
         </is>
       </c>
     </row>
@@ -3930,270 +3932,359 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>[dbl_issue=1, col_guard=1]</t>
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="21" t="inlineStr">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rhit &amp; rdwr_ready &amp; tccd_ok &amp; twtr_ok &amp; !dbl_issue &amp; !col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>wr_col_m[e]  (given wr_sch_valid_i[e] &amp;&amp; wr_commit_ready)</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>wr_col_m[e] = whit &amp;&amp; r_bank_rdwr_ready[wb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; trtw_ok_i &amp;&amp; wr_commit_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [wr_commit_ready_i factored out; dbl_issue = (f_ap(wb) &amp;&amp; w_col_inflight_bank[wb]) | w_wr_col_inflight_ent[e]; col_guard = r_ap_closing[wb] | w_ref_col_block[wb] | w_wr_turn_block | w_ap_col_guard[wb] | w_pre_col_guard[wb] | w_preact_bank_guard[wb]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = dbl_issue/col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) dbl_issue and col_guard are independent: the first is double-issue prevention for THIS entry/bank, the second folds turnaround, AP and precharge guards. Either can hold alone.</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:581-587</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Exact mirror of rd_col_m with the write-side turnaround (trtw) and commit-ready: 1s only on [dbl_issue=0, col_guard=0].</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C102" s="21" t="inlineStr">
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D102" s="21" t="inlineStr">
+      <c r="D113" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E102" s="21" t="inlineStr">
+      <c r="E113" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="21" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="inlineStr">
+      <c r="B114" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B104" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B105" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B106" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>w_rd_turn_block / w_wr_turn_block</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="18" t="inlineStr">
-        <is>
-          <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="21" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=0, col_guard=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C120" s="21" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B117" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="21" t="inlineStr">
+      <c r="D120" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B118" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="21" t="inlineStr">
+      <c r="E120" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B119" s="22" t="n">
-        <v>1</v>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
-        </is>
-      </c>
-      <c r="D122" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
-        </is>
+      <c r="A122" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="18" t="inlineStr">
-        <is>
-          <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; tfaw_ok_i &amp;&amp; trrd_ok_i &amp;&amp; !w_rfc_busy   [wr_act_m[e] is the same with wb for rb]</t>
-        </is>
+      <c r="A123" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
+      <c r="A124" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=1, col_guard=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D127" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=0]</t>
-        </is>
+      <c r="A128" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C129" s="21" t="inlineStr">
+      <c r="A129" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D129" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E129" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="21" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B130" s="23" t="n">
@@ -4212,93 +4303,93 @@
     <row r="131">
       <c r="A131" s="21" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>[dbl_issue=1, col_guard=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="21" t="inlineStr">
+      <c r="D134" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="21" t="inlineStr">
+      <c r="E134" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B133" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=1]</t>
-        </is>
+      <c r="A135" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C136" s="21" t="inlineStr">
+      <c r="A136" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D136" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E136" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="21" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B137" s="23" t="n">
@@ -4317,7 +4408,7 @@
     <row r="138">
       <c r="A138" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B138" s="23" t="n">
@@ -4333,1039 +4424,1626 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="140">
-      <c r="A140" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B140" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="23" t="n">
-        <v>0</v>
+      <c r="A140" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    whit &amp; rdwr_ready &amp; tccd_ok &amp; trtw_ok &amp; !dbl_issue &amp; !col_guard</t>
+        </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=1, rfc_busy=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C143" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D143" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E143" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B144" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" s="23" t="n">
-        <v>0</v>
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>w_rd_turn_block / w_wr_turn_block</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
+        </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B145" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="23" t="n">
-        <v>0</v>
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
+        </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B146" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="23" t="n">
-        <v>0</v>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
+        </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B147" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" s="23" t="n">
-        <v>0</v>
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) The two fire flags are consecutive pipeline stages of the same event, so all four combinations occur as a fired column walks through: 01 means 'fired last cycle', 11 'two back to back'.</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (r_wrfire0/r_wrfire1)</t>
+        </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=1, rfc_busy=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C150" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D150" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E150" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="A149" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B151" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" s="23" t="n">
-        <v>0</v>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B152" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="21" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B153" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="23" t="n">
-        <v>0</v>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B153" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B154" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B154" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" s="23" t="n">
-        <v>0</v>
+      <c r="B155" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="15" t="inlineStr">
-        <is>
-          <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
-        </is>
-      </c>
-      <c r="D157" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (classify)</t>
+      <c r="A157" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="18" t="inlineStr">
-        <is>
-          <t>rd_pre_m[e] = r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; !rhit &amp;&amp; r_bank_pre_ready[rb]   [wr_pre_m[e] is the same with wb/whit]</t>
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    oppfire1  |  oppfire0</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>rows = row_active/guarded   cols = hit/pre_ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="24" t="inlineStr">
+      <c r="A159" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
+        </is>
+      </c>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; tfaw_ok_i &amp;&amp; trrd_ok_i &amp;&amp; !w_rfc_busy   [wr_act_m[e] is the same with wb for rb]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="19" t="inlineStr">
         <is>
           <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    hit =&gt; row_active. A row HIT is defined as 'this bank has a row open AND it is the requested one', so a hit with no open row is not a state the hardware can be in -- it is a contradiction in the term itself, not a case the logic happens to avoid.</t>
-        </is>
-      </c>
-      <c r="D161" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:562-565 (rhit/whit = r_bank_row_active[b] &amp;&amp; row==open_row)</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    pre_ready =&gt; row_active. safe_pre_o is ANDed with r_row_valid, so tRAS/tRTP/tWR clearance is only ever reported for a bank that has a row to precharge.</t>
-        </is>
-      </c>
-      <c r="D162" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:138 (safe_pre_o = r_row_valid &amp;&amp; (r_ras=='0) &amp;&amp; (r_preblk=='0) &amp;&amp; !r_ap_pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
-        </is>
-      </c>
-    </row>
     <row r="165">
-      <c r="B165" s="21" t="inlineStr">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    act_ready =&gt; !row_active. bank_act_ready is safe_act_o, which is ANDed with !r_row_valid -- a bank with a row open never reports itself ready to activate. Half the grid cannot occur.</t>
+        </is>
+      </c>
+      <c r="D165" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:133 (safe_act_o = !r_row_valid &amp;&amp; ...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C165" s="21" t="inlineStr">
+      <c r="C169" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D165" s="21" t="inlineStr">
+      <c r="D169" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E165" s="21" t="inlineStr">
+      <c r="E169" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="21" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B166" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C166" s="25" t="inlineStr">
+      <c r="B170" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B172" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D166" s="25" t="inlineStr">
+      <c r="E172" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E166" s="25" t="inlineStr">
+    </row>
+    <row r="173">
+      <c r="A173" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B173" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="21" t="inlineStr">
+      <c r="E173" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C176" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B167" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C167" s="25" t="inlineStr">
+      <c r="D176" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E176" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B177" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D167" s="25" t="inlineStr">
+      <c r="E179" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E167" s="25" t="inlineStr">
+    </row>
+    <row r="180">
+      <c r="A180" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="21" t="inlineStr">
+      <c r="E180" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C183" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D183" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B168" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C168" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="21" t="inlineStr">
+      <c r="E183" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-      <c r="B169" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C169" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="20" t="inlineStr">
-        <is>
-          <t>cells: 10 reachable, 6 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="15" t="inlineStr">
-        <is>
-          <t>w_guarded[b]</t>
-        </is>
-      </c>
-      <c r="D173" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (guard fold)</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="18" t="inlineStr">
-        <is>
-          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = r_bank==b]</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>rows = guard0/guard1   cols = pick_guards_nz/inflight_rowop_or_col   pages = bank_match</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>[bank_match=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="B180" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C180" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D180" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E180" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B181" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B182" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C182" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B183" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C183" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D183" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B184" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C184" s="22" t="n">
-        <v>1</v>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B184" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="D184" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E184" s="22" t="n">
-        <v>1</v>
+      <c r="E184" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>[bank_match=1]</t>
+      <c r="A186" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E186" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="B187" s="21" t="inlineStr">
+      <c r="A187" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E187" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=1, rfc_busy=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C187" s="21" t="inlineStr">
+      <c r="C190" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D187" s="21" t="inlineStr">
+      <c r="D190" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E187" s="21" t="inlineStr">
+      <c r="E190" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B188" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D188" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B189" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C189" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D189" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E189" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B190" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C190" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D190" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E190" s="22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="21" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B193" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E193" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B191" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C191" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D191" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E191" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="15" t="inlineStr">
-        <is>
-          <t>w_out_ready / w_fire_out</t>
-        </is>
-      </c>
-      <c r="D194" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (output register)</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="18" t="inlineStr">
-        <is>
-          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+      <c r="B194" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E194" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>cells: 48 reachable, 16 don't-care (X) of 64. Read the CHECK over the reachable cells only.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="19" t="inlineStr">
         <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="B200" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A198" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    !guarded &amp; act_ready &amp; tfaw_ok &amp; trrd_ok &amp; !rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="21" t="inlineStr">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
+        </is>
+      </c>
+      <c r="D201" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>rd_pre_m[e] = r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; !rhit &amp;&amp; r_bank_pre_ready[rb]   [wr_pre_m[e] is the same with wb/whit]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>rows = row_active/guarded   cols = hit/pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    hit =&gt; row_active. A row HIT is defined as 'this bank has a row open AND it is the requested one', so a hit with no open row is not a state the hardware can be in -- it is a contradiction in the term itself, not a case the logic happens to avoid.</t>
+        </is>
+      </c>
+      <c r="D205" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:562-565 (rhit/whit = r_bank_row_active[b] &amp;&amp; row==open_row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    pre_ready =&gt; row_active. safe_pre_o is ANDed with r_row_valid, so tRAS/tRTP/tWR clearance is only ever reported for a bank that has a row to precharge.</t>
+        </is>
+      </c>
+      <c r="D206" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:138 (safe_pre_o = r_row_valid &amp;&amp; (r_ras=='0) &amp;&amp; (r_preblk=='0) &amp;&amp; !r_ap_pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B201" s="22" t="n">
+      <c r="C209" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D209" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E209" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B210" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D210" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E210" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B211" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C211" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D211" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E211" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B212" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C212" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B213" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C213" s="22" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B202" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B203" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B204" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="15" t="inlineStr">
-        <is>
-          <t>pick priority (strict, first match wins)</t>
-        </is>
-      </c>
-      <c r="D207" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="20" t="inlineStr">
-        <is>
-          <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="26" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B209" s="26" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="C209" s="26" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="D209" s="26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B210" s="27" t="inlineStr">
-        <is>
-          <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
-        </is>
-      </c>
-      <c r="C210" s="27" t="inlineStr">
-        <is>
-          <t>forward init op</t>
-        </is>
-      </c>
-      <c r="D210" s="27" t="inlineStr">
-        <is>
-          <t>MRS/PRE/REF from init_sequencer verbatim</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B211" s="27" t="inlineStr">
-        <is>
-          <t>refresh_req_i || refresh_drain_i</t>
-        </is>
-      </c>
-      <c r="C211" s="27" t="inlineStr">
-        <is>
-          <t>refresh branch</t>
-        </is>
-      </c>
-      <c r="D211" s="27" t="inlineStr">
-        <is>
-          <t>see refresh-branch K-map; never falls through while pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B212" s="27" t="inlineStr">
-        <is>
-          <t>rd_col_f</t>
-        </is>
-      </c>
-      <c r="C212" s="27" t="inlineStr">
-        <is>
-          <t>RD/RDA row-hit</t>
-        </is>
-      </c>
-      <c r="D212" s="27" t="inlineStr">
-        <is>
-          <t>read priority over write</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B213" s="27" t="inlineStr">
-        <is>
-          <t>wr_col_f</t>
-        </is>
-      </c>
-      <c r="C213" s="27" t="inlineStr">
-        <is>
-          <t>WR/WRA row-hit</t>
-        </is>
-      </c>
-      <c r="D213" s="27" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B214" s="27" t="inlineStr">
-        <is>
-          <t>rd_act_f</t>
-        </is>
-      </c>
-      <c r="C214" s="27" t="inlineStr">
-        <is>
-          <t>ACT for oldest pending read</t>
-        </is>
-      </c>
-      <c r="D214" s="27" t="inlineStr">
-        <is>
-          <t>bank-parallel</t>
-        </is>
+      <c r="D213" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B215" s="27" t="inlineStr">
-        <is>
-          <t>wr_act_f</t>
-        </is>
-      </c>
-      <c r="C215" s="27" t="inlineStr">
-        <is>
-          <t>ACT for oldest pending write</t>
-        </is>
-      </c>
-      <c r="D215" s="27" t="inlineStr"/>
+      <c r="A215" s="20" t="inlineStr">
+        <is>
+          <t>cells: 10 reachable, 6 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B216" s="27" t="inlineStr">
-        <is>
-          <t>rd_pre_f</t>
-        </is>
-      </c>
-      <c r="C216" s="27" t="inlineStr">
-        <is>
-          <t>PRE wrong-row bank (read)</t>
-        </is>
-      </c>
-      <c r="D216" s="27" t="inlineStr"/>
+      <c r="A216" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="B217" s="27" t="inlineStr">
-        <is>
-          <t>wr_pre_f</t>
-        </is>
-      </c>
-      <c r="C217" s="27" t="inlineStr">
-        <is>
-          <t>PRE wrong-row bank (write)</t>
-        </is>
-      </c>
-      <c r="D217" s="27" t="inlineStr"/>
+      <c r="A217" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    !guarded &amp; !hit &amp; pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="15" t="inlineStr">
         <is>
+          <t>w_guarded[b]</t>
+        </is>
+      </c>
+      <c r="D220" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="18" t="inlineStr">
+        <is>
+          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = r_bank==b]</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>rows = guard0/guard1   cols = pick_guards_nz/inflight_rowop_or_col   pages = bank_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    guard0 / guard1</t>
+        </is>
+      </c>
+      <c r="B224" s="16" t="inlineStr">
+        <is>
+          <t>r_guard0[b] / r_guard1[b] -- the two registered guard stages a pick walks through</t>
+        </is>
+      </c>
+      <c r="D224" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    pick_guards_nz</t>
+        </is>
+      </c>
+      <c r="B225" s="16" t="inlineStr">
+        <is>
+          <t>w_prepick_guard[b] | w_col_inflight_guard[b]</t>
+        </is>
+      </c>
+      <c r="D225" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:346-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    inflight_rowop_or_col</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
+          <t>w_inflight_preact || w_inflight_col</t>
+        </is>
+      </c>
+      <c r="D226" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:300-302</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    bank_match</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="inlineStr">
+        <is>
+          <t>r_bank == b -- the in-flight pick targets THIS bank</t>
+        </is>
+      </c>
+      <c r="D227" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) The guard stages are a shift register, so guard0/guard1 take all four combinations as a pick moves through; bank_match is an address compare independent of all of them.</t>
+        </is>
+      </c>
+      <c r="D229" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>[bank_match=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C233" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D233" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E233" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B234" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B235" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B236" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B237" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>[bank_match=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C240" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D240" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E240" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B241" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B242" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B243" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B244" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    pick_guards_nz  |  guard1  |  guard0  |  inflight_rowop_or_col &amp; bank_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="15" t="inlineStr">
+        <is>
+          <t>w_out_ready / w_fire_out</t>
+        </is>
+      </c>
+      <c r="D250" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (output register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="18" t="inlineStr">
+        <is>
+          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) pick_valid is internal; cmd_ready_i belongs to the downstream FIFO. Nothing couples them, so all four occur -- which is what makes the pick pipeline latency rather than a rate limit.</t>
+        </is>
+      </c>
+      <c r="D254" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (output register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B258" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B259" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B260" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B261" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="15" t="inlineStr">
+        <is>
+          <t>pick priority (strict, first match wins)</t>
+        </is>
+      </c>
+      <c r="D267" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="20" t="inlineStr">
+        <is>
+          <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="25" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B269" s="25" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C269" s="25" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D269" s="25" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B270" s="26" t="inlineStr">
+        <is>
+          <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
+        </is>
+      </c>
+      <c r="C270" s="26" t="inlineStr">
+        <is>
+          <t>forward init op</t>
+        </is>
+      </c>
+      <c r="D270" s="26" t="inlineStr">
+        <is>
+          <t>MRS/PRE/REF from init_sequencer verbatim</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B271" s="26" t="inlineStr">
+        <is>
+          <t>refresh_req_i || refresh_drain_i</t>
+        </is>
+      </c>
+      <c r="C271" s="26" t="inlineStr">
+        <is>
+          <t>refresh branch</t>
+        </is>
+      </c>
+      <c r="D271" s="26" t="inlineStr">
+        <is>
+          <t>see refresh-branch K-map; never falls through while pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B272" s="26" t="inlineStr">
+        <is>
+          <t>rd_col_f</t>
+        </is>
+      </c>
+      <c r="C272" s="26" t="inlineStr">
+        <is>
+          <t>RD/RDA row-hit</t>
+        </is>
+      </c>
+      <c r="D272" s="26" t="inlineStr">
+        <is>
+          <t>read priority over write</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B273" s="26" t="inlineStr">
+        <is>
+          <t>wr_col_f</t>
+        </is>
+      </c>
+      <c r="C273" s="26" t="inlineStr">
+        <is>
+          <t>WR/WRA row-hit</t>
+        </is>
+      </c>
+      <c r="D273" s="26" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B274" s="26" t="inlineStr">
+        <is>
+          <t>rd_act_f</t>
+        </is>
+      </c>
+      <c r="C274" s="26" t="inlineStr">
+        <is>
+          <t>ACT for oldest pending read</t>
+        </is>
+      </c>
+      <c r="D274" s="26" t="inlineStr">
+        <is>
+          <t>bank-parallel</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B275" s="26" t="inlineStr">
+        <is>
+          <t>wr_act_f</t>
+        </is>
+      </c>
+      <c r="C275" s="26" t="inlineStr">
+        <is>
+          <t>ACT for oldest pending write</t>
+        </is>
+      </c>
+      <c r="D275" s="26" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B276" s="26" t="inlineStr">
+        <is>
+          <t>rd_pre_f</t>
+        </is>
+      </c>
+      <c r="C276" s="26" t="inlineStr">
+        <is>
+          <t>PRE wrong-row bank (read)</t>
+        </is>
+      </c>
+      <c r="D276" s="26" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B277" s="26" t="inlineStr">
+        <is>
+          <t>wr_pre_f</t>
+        </is>
+      </c>
+      <c r="C277" s="26" t="inlineStr">
+        <is>
+          <t>PRE wrong-row bank (write)</t>
+        </is>
+      </c>
+      <c r="D277" s="26" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="15" t="inlineStr">
+        <is>
           <t>r_rfc_cnt next-value</t>
         </is>
       </c>
-      <c r="D220" s="17" t="inlineStr">
+      <c r="D280" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="20" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="20" t="inlineStr">
         <is>
           <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="26" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="25" t="inlineStr">
         <is>
           <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
         </is>
       </c>
-      <c r="B222" s="26" t="inlineStr">
+      <c r="B282" s="25" t="inlineStr">
         <is>
           <t>r_rfc_cnt != 0</t>
         </is>
       </c>
-      <c r="C222" s="26" t="inlineStr">
+      <c r="C282" s="25" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="27" t="inlineStr">
+    <row r="283">
+      <c r="A283" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B223" s="27" t="inlineStr">
+      <c r="B283" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C223" s="27" t="inlineStr">
+      <c r="C283" s="26" t="inlineStr">
         <is>
           <t>t_rfc_i (load)</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="27" t="inlineStr">
+    <row r="284">
+      <c r="A284" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B224" s="27" t="inlineStr">
+      <c r="B284" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C224" s="27" t="inlineStr">
+      <c r="C284" s="26" t="inlineStr">
         <is>
           <t>r_rfc_cnt - 1</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="27" t="inlineStr">
+    <row r="285">
+      <c r="A285" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B225" s="27" t="inlineStr">
+      <c r="B285" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C225" s="27" t="inlineStr">
+      <c r="C285" s="26" t="inlineStr">
         <is>
           <t>0 (idle)</t>
         </is>
@@ -5382,7 +6060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5438,379 +6116,397 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tRP counting =&gt; row closed. The PRE edge loads tRP and clears row_valid together, so (row_valid=1, rp!=0) cannot occur.</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:106 + :120-123</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (0,1,1): closed row, tRP and tRC elapsed. Any 1 with row_valid=1 would re-ACT an open bank.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="21" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="22" t="n">
-        <v>1</v>
+      <c r="C12" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="23" t="n">
-        <v>0</v>
+      <c r="C13" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>0</v>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>cells: 6 reachable, 2 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    !row_valid &amp; rp==0 &amp; rc==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>safe_rd_o / safe_wr_o</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:135-136</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>safe_rd = safe_wr = r_row_valid &amp;&amp; (r_rcd == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd==0   cols = ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tRCD counting =&gt; row open. The ACT edge loads tRCD and sets row_valid together, so (row_valid=0, rcd!=0) cannot occur.</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:96 + :116</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). ap_pending=1 must kill columns — the row is committed to auto-close.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="21" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="B31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B32" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="C32" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>cells: 6 reachable, 2 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    row_valid &amp; rcd==0 &amp; !ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>safe_pre_o</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:138</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>safe_pre = r_row_valid &amp;&amp; (r_ras == 0) &amp;&amp; (r_preblk == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>rows = row_valid/ras==0   cols = preblk==0/ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tRAS counting =&gt; row open. tRAS loads on the ACT edge that sets row_valid, so (row_valid=0, ras!=0) cannot occur.</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv (set_act_i -&gt; r_ras) + :116</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="21" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D47" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E47" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>w_ap_fire (internal auto-precharge)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:88</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>w_ap_fire = r_ap_pending &amp;&amp; (r_preblk == 0) &amp;&amp; (r_ras == 0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>rows = ap_pending/preblk==0   cols = ras==0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B50" s="23" t="n">
@@ -5818,12 +6514,18 @@
       </c>
       <c r="C50" s="23" t="n">
         <v>0</v>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B51" s="23" t="n">
@@ -5832,106 +6534,90 @@
       <c r="C51" s="23" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>1</v>
+      <c r="D51" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>0</v>
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>cells: 12 reachable, 4 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    row_valid &amp; ras==0 &amp; preblk==0 &amp; !ap_pending</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>state_o (observability only)</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:144-147</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="inlineStr">
-        <is>
-          <t>rv ? (rcd_nz ? ACTIVATING : ACTIVE) : (rp_nz ? PRECHARGING : IDLE)</t>
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>rows = row_valid/rcd_nz   cols = rp_nz</t>
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>w_ap_fire (internal auto-precharge)</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:88</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>w_ap_fire = r_ap_pending &amp;&amp; (r_preblk == 0) &amp;&amp; (r_ras == 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>rows = ap_pending/preblk==0   cols = ras==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rcd_nz =&gt; row_valid. The ACT edge loads tRCD and sets row_valid together, and nothing else loads tRCD, so a bank counting tRCD always has its row marked open.</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:96 (set_act_i -&gt; r_rcd) + :116 (r_row_valid &lt;= 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rp_nz =&gt; !row_valid. The PRE edge (explicit or auto) loads tRP and clears row_valid together.</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:106 (set_pre_i||w_ap_fire -&gt; r_rp) + :120-123 (r_row_valid &lt;= 0)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Therefore rcd_nz and rp_nz are MUTUALLY EXCLUSIVE -- a bank cannot be inside tRCD and tRP at once. That single relation removes a quarter of this grid; drawing 0s there would assert the decode had been checked in a state the timers forbid.</t>
+          <t xml:space="preserve">    (independent) ap_pending is set by an AP column while the two timers run from the ACT and column edges, so a pending auto-precharge can sit through any combination of them. That is the flag's purpose.</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>bank_timer.sv:96,106,116,120-123</t>
+          <t>bank_timer.sv:88 + :115-127</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
         </is>
       </c>
     </row>
@@ -5953,11 +6639,11 @@
           <t>00</t>
         </is>
       </c>
-      <c r="B66" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="22" t="n">
-        <v>1</v>
+      <c r="B66" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5966,15 +6652,11 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B67" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C67" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="B67" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5983,13 +6665,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B68" s="22" t="n">
+      <c r="B68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="22" t="n">
         <v>1</v>
-      </c>
-      <c r="C68" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -5998,228 +6678,416 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B69" s="22" t="n">
+      <c r="B69" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ap_pending &amp; preblk==0 &amp; ras==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>state_o (observability only)</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:144-147</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>rv ? (rcd_nz ? ACTIVATING : ACTIVE) : (rp_nz ? PRECHARGING : IDLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>rows = row_valid/rcd_nz   cols = rp_nz</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rcd_nz =&gt; row_valid. The ACT edge loads tRCD and sets row_valid together, and nothing else loads tRCD, so a bank counting tRCD always has its row marked open.</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:96 (set_act_i -&gt; r_rcd) + :116 (r_row_valid &lt;= 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rp_nz =&gt; !row_valid. The PRE edge (explicit or auto) loads tRP and clears row_valid together.</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:106 (set_pre_i||w_ap_fire -&gt; r_rp) + :120-123 (r_row_valid &lt;= 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Therefore rcd_nz and rp_nz are MUTUALLY EXCLUSIVE -- a bank cannot be inside tRCD and tRP at once. That single relation removes a quarter of this grid; drawing 0s there would assert the decode had been checked in a state the timers forbid.</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:96,106,116,120-123</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C69" s="25" t="inlineStr">
+      <c r="C85" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
         <is>
           <t>cells: 4 reachable, 4 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="15" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
         <is>
           <t>row_valid / ap_pending next-state priority</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D95" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:115-127</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>Strict priority ACT &gt; PRE &gt; auto-PRE &gt; column. The arbiter never issues ACT and PRE to one bank in one cycle (single-issue), so rows 1-2 cannot conflict in practice.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="26" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="25" t="inlineStr">
         <is>
           <t>set_act</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr">
+      <c r="B97" s="25" t="inlineStr">
         <is>
           <t>set_pre</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
+      <c r="C97" s="25" t="inlineStr">
         <is>
           <t>w_ap_fire</t>
         </is>
       </c>
-      <c r="D75" s="26" t="inlineStr">
+      <c r="D97" s="25" t="inlineStr">
         <is>
           <t>set_rd||set_wr</t>
         </is>
       </c>
-      <c r="E75" s="26" t="inlineStr">
+      <c r="E97" s="25" t="inlineStr">
         <is>
           <t>row_valid'</t>
         </is>
       </c>
-      <c r="F75" s="26" t="inlineStr">
+      <c r="F97" s="25" t="inlineStr">
         <is>
           <t>ap_pending'</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="27" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B76" s="27" t="inlineStr">
+      <c r="B98" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C76" s="27" t="inlineStr">
+      <c r="C98" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D76" s="27" t="inlineStr">
+      <c r="D98" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E76" s="27" t="inlineStr">
+      <c r="E98" s="26" t="inlineStr">
         <is>
           <t>1 (row=row_i)</t>
         </is>
       </c>
-      <c r="F76" s="27" t="inlineStr">
+      <c r="F98" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="27" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B77" s="27" t="inlineStr">
+      <c r="B99" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C77" s="27" t="inlineStr">
+      <c r="C99" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D77" s="27" t="inlineStr">
+      <c r="D99" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E77" s="27" t="inlineStr">
+      <c r="E99" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F77" s="27" t="inlineStr">
+      <c r="F99" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="27" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B78" s="27" t="inlineStr">
+      <c r="B100" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C78" s="27" t="inlineStr">
+      <c r="C100" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D78" s="27" t="inlineStr">
+      <c r="D100" s="26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E78" s="27" t="inlineStr">
+      <c r="E100" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F78" s="27" t="inlineStr">
+      <c r="F100" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="27" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B79" s="27" t="inlineStr">
+      <c r="B101" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C79" s="27" t="inlineStr">
+      <c r="C101" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D79" s="27" t="inlineStr">
+      <c r="D101" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E79" s="27" t="inlineStr">
+      <c r="E101" s="26" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F79" s="27" t="inlineStr">
+      <c r="F101" s="26" t="inlineStr">
         <is>
           <t>set_ap_i</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="27" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B80" s="27" t="inlineStr">
+      <c r="B102" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C80" s="27" t="inlineStr">
+      <c r="C102" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D80" s="27" t="inlineStr">
+      <c r="D102" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E80" s="27" t="inlineStr">
+      <c r="E102" s="26" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F80" s="27" t="inlineStr">
+      <c r="F102" s="26" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
@@ -7737,7 +8605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7793,38 +8661,40 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) grant does NOT imply pend_nz. An EARLY grant -- the scheduler pulsing while pending is zero -- is an explicitly handled case (w_grant_early), so the (1,0) cell is reachable and must read 0, not X. Checked, and genuinely independent.</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>refresh_ctrl.sv:133-134</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a grant with nothing pending is swallowed (the accumulator never goes negative).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="21" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
@@ -7834,367 +8704,464 @@
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
-        <v>1</v>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B15" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    grant &amp; pend_nz</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>refresh_drain_active</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:126</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0) &amp;&amp; refresh_req_o</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>rows = rem_nz/pend_nz   cols = req_o</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) req_o does NOT follow pend_nz: a postponed backlog withholds the registered request while pending is non-zero. That is exactly why the term is in the equation, so all combinations occur.</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>refresh_ctrl.sv:186-192</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): holding the arbiter in the refresh branch requires quota AND owed refreshes AND the REGISTERED request. The req_o term is not redundant -- a postponed backlog withholds req_o while pending is non-zero, and without this term the drain window would open anyway and defeat the postpone credit.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="21" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="B29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="B30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="22" t="n">
+      <c r="B31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rem_nz &amp; pend_nz &amp; req_o</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>r_pending next-value</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:98-108</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>refresh_req_o (registered) = pending&gt;0. Saturation at 8 = a JEDEC retention violation looming — the arbiter must be serving REFs.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>enable &amp;&amp; expired</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>w_grant_accept</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>min(pending+1, 8)  (postpone cap)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>pending-1</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>pending (net zero)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>busy_o</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>pumice_mem_cmd_scheduler.sv</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>busy = !init_done || refresh_req || w_cmd_rd_valid || (|w_bank_row_active[0])</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>rows = init_done/refresh_req   cols = cmd_rd_valid/any_row_active</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS: none stated -- every combination is treated as reachable. If two of these axes are in fact related, the map is over-claiming (PUMICE-KMAP).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) cmd_rd_valid is the command FIFO's read-valid and is not gated on init_done, and any_row_active is a registered image, so all sixteen combinations are reachable.</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>pumice_mem_cmd_scheduler.sv:527,574</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="21" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C54" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D45" s="21" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="E54" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B46" s="22" t="n">
+      <c r="B55" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="22" t="n">
+      <c r="C55" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="22" t="n">
+      <c r="D55" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="22" t="n">
+      <c r="E55" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B47" s="22" t="n">
+      <c r="B56" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="22" t="n">
+      <c r="C56" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="22" t="n">
+      <c r="D56" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="22" t="n">
+      <c r="E56" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B48" s="22" t="n">
+      <c r="B57" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C57" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="22" t="n">
+      <c r="D57" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="22" t="n">
+      <c r="E57" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="22" t="n">
+      <c r="B58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="22" t="n">
+      <c r="D58" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="22" t="n">
+      <c r="E58" s="22" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    any_row_active  |  cmd_rd_valid  |  refresh_req  |  !init_done</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+        </is>
       </c>
     </row>
   </sheetData>
